--- a/src/attributions/attributions_ig_traj_71.xlsx
+++ b/src/attributions/attributions_ig_traj_71.xlsx
@@ -999,52 +999,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.4127031711776176</v>
+        <v>0.08084159318537318</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.05690190231463328</v>
+        <v>-0.01665186807646355</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.03625286754765598</v>
+        <v>-0.01073640882102607</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H2" t="n">
         <v>-0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2248478862780798</v>
+        <v>0.06583982010630716</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0.09820113333180117</v>
+        <v>0.03638115508003625</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.04246957159804594</v>
+        <v>-0.008964057841491804</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -1053,19 +1053,19 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2230236719606297</v>
+        <v>0.03697776940807274</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.1279477116445038</v>
+        <v>-0.0273428255851283</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.009708743050271963</v>
+        <v>-0.02847797698005345</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -1074,58 +1074,58 @@
         <v>-0</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.05035537280385224</v>
+        <v>-0.007557186180122494</v>
       </c>
       <c r="AD2" t="n">
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0.0120270260756071</v>
+        <v>-0.01255530081681403</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.01535634631358993</v>
+        <v>-0.01582326023097363</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.1083131017027298</v>
+        <v>0.06038588319619952</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN2" t="n">
-        <v>-0.1050602767801769</v>
+        <v>-0.01591609198697994</v>
       </c>
       <c r="AO2" t="n">
-        <v>-0.04176025313451581</v>
+        <v>0.02583040395897251</v>
       </c>
       <c r="AP2" t="n">
         <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR2" t="n">
         <v>-0</v>
@@ -1137,43 +1137,43 @@
         <v>-0</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.000861100623007</v>
+        <v>0.209384448011757</v>
       </c>
       <c r="AV2" t="n">
         <v>-0</v>
       </c>
       <c r="AW2" t="n">
-        <v>-0.06361077818767387</v>
+        <v>-0.0749818385998986</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.3915403579112831</v>
+        <v>-0.07995768091080613</v>
       </c>
       <c r="AY2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC2" t="n">
         <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.003855741610270664</v>
+        <v>-0.00262553511987774</v>
       </c>
       <c r="BE2" t="n">
         <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>-0.01331763221565981</v>
+        <v>-0.002094740394666356</v>
       </c>
       <c r="BG2" t="n">
-        <v>-1.429153548298366e-10</v>
+        <v>-7.324885964494665e-12</v>
       </c>
       <c r="BH2" t="n">
         <v>0</v>
@@ -1182,7 +1182,7 @@
         <v>-0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK2" t="n">
         <v>0</v>
@@ -1191,22 +1191,22 @@
         <v>-0</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.01416658987602956</v>
+        <v>-0.001586820142435869</v>
       </c>
       <c r="BN2" t="n">
         <v>-0</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.3244911791032239</v>
+        <v>0.0171513217544346</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.09883958823290985</v>
+        <v>0.05124293451098573</v>
       </c>
       <c r="BQ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
         <v>-0</v>
@@ -1218,25 +1218,25 @@
         <v>-0</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.5141965294804587</v>
+        <v>0.1446813069488182</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX2" t="n">
-        <v>-0.01087327576287799</v>
+        <v>-0.02874527465377088</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.0404122102218261</v>
+        <v>-0.01650470545211131</v>
       </c>
       <c r="BZ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA2" t="n">
         <v>-0</v>
       </c>
       <c r="CB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC2" t="n">
         <v>0</v>
@@ -1245,46 +1245,46 @@
         <v>-0</v>
       </c>
       <c r="CE2" t="n">
-        <v>-0.2533161267306074</v>
+        <v>-0.0716941722374967</v>
       </c>
       <c r="CF2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG2" t="n">
-        <v>0.02182194211471374</v>
+        <v>0.05228876462969425</v>
       </c>
       <c r="CH2" t="n">
-        <v>-0.04009131319742689</v>
+        <v>0.008390155085624648</v>
       </c>
       <c r="CI2" t="n">
         <v>-0</v>
       </c>
       <c r="CJ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK2" t="n">
         <v>0</v>
       </c>
       <c r="CL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM2" t="n">
         <v>0</v>
       </c>
       <c r="CN2" t="n">
-        <v>0.02314340061250843</v>
+        <v>-0.04778594482059721</v>
       </c>
       <c r="CO2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP2" t="n">
-        <v>-0.2072025075942485</v>
+        <v>0.06656552986612238</v>
       </c>
       <c r="CQ2" t="n">
-        <v>-0.2585733321816564</v>
+        <v>0.036626922245917</v>
       </c>
       <c r="CR2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS2" t="n">
         <v>-0</v>
@@ -1293,55 +1293,55 @@
         <v>-0</v>
       </c>
       <c r="CU2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW2" t="n">
-        <v>-0.2087891667803326</v>
+        <v>-0.07642760854274873</v>
       </c>
       <c r="CX2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY2" t="n">
-        <v>0.1427641989120399</v>
+        <v>0.0593575759437142</v>
       </c>
       <c r="CZ2" t="n">
-        <v>-0.03325934428659269</v>
+        <v>0.0126967596840444</v>
       </c>
       <c r="DA2" t="n">
         <v>0</v>
       </c>
       <c r="DB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC2" t="n">
         <v>-0</v>
       </c>
       <c r="DD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE2" t="n">
         <v>0</v>
       </c>
       <c r="DF2" t="n">
-        <v>-0.09118934816345542</v>
+        <v>-0.02746698434244862</v>
       </c>
       <c r="DG2" t="n">
         <v>0</v>
       </c>
       <c r="DH2" t="n">
-        <v>-0.0151216365679489</v>
+        <v>-0.005663423930109625</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.02891645457265534</v>
+        <v>-0.00571183997766428</v>
       </c>
       <c r="DJ2" t="n">
         <v>-0</v>
       </c>
       <c r="DK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL2" t="n">
         <v>0</v>
@@ -1353,19 +1353,19 @@
         <v>-0</v>
       </c>
       <c r="DO2" t="n">
-        <v>-0.1586704329716081</v>
+        <v>-0.04150691803222487</v>
       </c>
       <c r="DP2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ2" t="n">
-        <v>0.1192197800942425</v>
+        <v>0.013213248331239</v>
       </c>
       <c r="DR2" t="n">
-        <v>-0.05745434424322614</v>
+        <v>-0.03229685439045296</v>
       </c>
       <c r="DS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT2" t="n">
         <v>-0</v>
@@ -1380,22 +1380,22 @@
         <v>-0</v>
       </c>
       <c r="DX2" t="n">
-        <v>0.04851626484434605</v>
+        <v>0.02717731711718502</v>
       </c>
       <c r="DY2" t="n">
         <v>0</v>
       </c>
       <c r="DZ2" t="n">
-        <v>-0.08047796932129699</v>
+        <v>0.04289260208987294</v>
       </c>
       <c r="EA2" t="n">
-        <v>-0.1157231347558257</v>
+        <v>-0.02135849142702141</v>
       </c>
       <c r="EB2" t="n">
         <v>-0</v>
       </c>
       <c r="EC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED2" t="n">
         <v>0</v>
@@ -1407,16 +1407,16 @@
         <v>0</v>
       </c>
       <c r="EG2" t="n">
-        <v>-0.08762734086497324</v>
+        <v>-0.05289136006681987</v>
       </c>
       <c r="EH2" t="n">
         <v>-0</v>
       </c>
       <c r="EI2" t="n">
-        <v>0.03570766267084803</v>
+        <v>0.05004599807438937</v>
       </c>
       <c r="EJ2" t="n">
-        <v>0.01744139595265198</v>
+        <v>0.01225947397456602</v>
       </c>
       <c r="EK2" t="n">
         <v>0</v>
@@ -1425,31 +1425,31 @@
         <v>-0</v>
       </c>
       <c r="EM2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO2" t="n">
         <v>0</v>
       </c>
       <c r="EP2" t="n">
-        <v>-0.2124938241372326</v>
+        <v>-0.04670032886563385</v>
       </c>
       <c r="EQ2" t="n">
         <v>-0</v>
       </c>
       <c r="ER2" t="n">
-        <v>-0.1857099665259852</v>
+        <v>-0.03712114286542226</v>
       </c>
       <c r="ES2" t="n">
-        <v>-0.06786557474465564</v>
+        <v>0.002296537440310446</v>
       </c>
       <c r="ET2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV2" t="n">
         <v>0</v>
@@ -1461,43 +1461,43 @@
         <v>-0</v>
       </c>
       <c r="EY2" t="n">
-        <v>-0.2093988998812409</v>
+        <v>-0.08211344650902157</v>
       </c>
       <c r="EZ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA2" t="n">
-        <v>0.07916590476949972</v>
+        <v>0.05777982049101279</v>
       </c>
       <c r="FB2" t="n">
-        <v>-0.05780351543490069</v>
+        <v>0.005802453351180677</v>
       </c>
       <c r="FC2" t="n">
         <v>-0</v>
       </c>
       <c r="FD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH2" t="n">
-        <v>-0.04992021122551019</v>
+        <v>-0.03084151990107148</v>
       </c>
       <c r="FI2" t="n">
         <v>-0</v>
       </c>
       <c r="FJ2" t="n">
-        <v>0.0764610374030492</v>
+        <v>0.01131285263985417</v>
       </c>
       <c r="FK2" t="n">
-        <v>-0.02435269250882383</v>
+        <v>0.004489935249095284</v>
       </c>
       <c r="FL2" t="n">
         <v>0</v>
@@ -1509,25 +1509,25 @@
         <v>-0</v>
       </c>
       <c r="FO2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ2" t="n">
-        <v>-0.08287061036770606</v>
+        <v>0.006720791460185567</v>
       </c>
       <c r="FR2" t="n">
         <v>-0</v>
       </c>
       <c r="FS2" t="n">
-        <v>-0.2569370024999116</v>
+        <v>0.08512285121454731</v>
       </c>
       <c r="FT2" t="n">
-        <v>-0.1438579055802192</v>
+        <v>-0.02519080945472593</v>
       </c>
       <c r="FU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV2" t="n">
         <v>-0</v>
@@ -1539,28 +1539,28 @@
         <v>0</v>
       </c>
       <c r="FY2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ2" t="n">
-        <v>-0.07520319924881154</v>
+        <v>-0.0663478523735684</v>
       </c>
       <c r="GA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB2" t="n">
-        <v>-0.1141049060738443</v>
+        <v>0.03084071958455021</v>
       </c>
       <c r="GC2" t="n">
         <v>0</v>
       </c>
       <c r="GD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE2" t="n">
         <v>-0</v>
       </c>
       <c r="GF2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG2" t="n">
         <v>-0</v>
@@ -2140,19 +2140,19 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>0.06054692297908712</v>
+        <v>0.07845958719229512</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.004962858446751363</v>
+        <v>0.005714360994938565</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.009327067721787758</v>
+        <v>-0.01314380998761341</v>
       </c>
       <c r="G4" t="n">
         <v>-0</v>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01740839010740642</v>
+        <v>0.1057414479665113</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -2176,79 +2176,79 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.01770712155301222</v>
+        <v>-0.006719732962493456</v>
       </c>
       <c r="O4" t="n">
-        <v>0.01959416487248501</v>
+        <v>0.01732251008679126</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.00142389435096405</v>
+        <v>0.02694387392484634</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.03366548464775485</v>
+        <v>-0.05352252265353059</v>
       </c>
       <c r="X4" t="n">
-        <v>0.02223273637611923</v>
+        <v>0.02402163422860046</v>
       </c>
       <c r="Y4" t="n">
         <v>-0</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB4" t="n">
         <v>-0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.005570910110996021</v>
+        <v>-0.00633375478735956</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.003937284265635508</v>
+        <v>-0.02036430761762286</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.001692969505605327</v>
+        <v>-0.001775212592359645</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
         <v>-0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.02186788235257284</v>
+        <v>0.04959497865588823</v>
       </c>
       <c r="AM4" t="n">
         <v>0</v>
@@ -2257,16 +2257,16 @@
         <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>-0.008976339558963105</v>
+        <v>0.001299500769277044</v>
       </c>
       <c r="AP4" t="n">
-        <v>-0.02085124571364804</v>
+        <v>-0.04675005310486205</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS4" t="n">
         <v>0</v>
@@ -2275,7 +2275,7 @@
         <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.1238490837799002</v>
+        <v>0.2566149749049058</v>
       </c>
       <c r="AV4" t="n">
         <v>0</v>
@@ -2284,52 +2284,52 @@
         <v>-0</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.01284802928248433</v>
+        <v>-0.05175134911434955</v>
       </c>
       <c r="AY4" t="n">
-        <v>-0.02313834507295645</v>
+        <v>-0.07439943685524873</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.006979338919762918</v>
+        <v>-0.01156506150913083</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF4" t="n">
         <v>0</v>
       </c>
       <c r="BG4" t="n">
-        <v>-0.005396454430300761</v>
+        <v>-0.01017488919732013</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.003901875369667214</v>
+        <v>0.007443550456427799</v>
       </c>
       <c r="BI4" t="n">
         <v>-0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.05337578588003426</v>
+        <v>0.01131720431213209</v>
       </c>
       <c r="BN4" t="n">
         <v>-0</v>
@@ -2338,37 +2338,37 @@
         <v>-0</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.01974532277029861</v>
+        <v>0.0783907288336825</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.01815131621871465</v>
+        <v>0.05718776939449183</v>
       </c>
       <c r="BR4" t="n">
         <v>-0</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT4" t="n">
         <v>0</v>
       </c>
       <c r="BU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.05293275797229256</v>
+        <v>0.147217459439044</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY4" t="n">
-        <v>-0.03746453770723494</v>
+        <v>-0.005168566073834289</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.04040667249748546</v>
+        <v>-0.02945321781779751</v>
       </c>
       <c r="CA4" t="n">
         <v>-0</v>
@@ -2383,22 +2383,22 @@
         <v>-0</v>
       </c>
       <c r="CE4" t="n">
-        <v>-0.006705792548174292</v>
+        <v>-0.0477057911359839</v>
       </c>
       <c r="CF4" t="n">
         <v>-0</v>
       </c>
       <c r="CG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH4" t="n">
-        <v>-0.00811002674604629</v>
+        <v>0.001234596065044397</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.02487266860219361</v>
+        <v>0.03344041851442861</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK4" t="n">
         <v>0</v>
@@ -2407,52 +2407,52 @@
         <v>-0</v>
       </c>
       <c r="CM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.01728289840186971</v>
+        <v>-0.02800814142912575</v>
       </c>
       <c r="CO4" t="n">
         <v>0</v>
       </c>
       <c r="CP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.0007409927440614448</v>
+        <v>0.09555316682091912</v>
       </c>
       <c r="CR4" t="n">
-        <v>-0.03932124355903557</v>
+        <v>0.02058996151015155</v>
       </c>
       <c r="CS4" t="n">
         <v>-0</v>
       </c>
       <c r="CT4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV4" t="n">
         <v>0</v>
       </c>
       <c r="CW4" t="n">
-        <v>-0.001278838462472816</v>
+        <v>-0.0421313553824729</v>
       </c>
       <c r="CX4" t="n">
         <v>0</v>
       </c>
       <c r="CY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CZ4" t="n">
-        <v>-0.007851053891543388</v>
+        <v>0.003696563485693133</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.03553457878818066</v>
+        <v>0.03716241383232658</v>
       </c>
       <c r="DB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC4" t="n">
         <v>-0</v>
@@ -2464,25 +2464,25 @@
         <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.009108135603307423</v>
+        <v>0.000585157860986865</v>
       </c>
       <c r="DG4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.01420671059401312</v>
+        <v>-0.03512257137592324</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.01899722047029486</v>
+        <v>0.05925796779002116</v>
       </c>
       <c r="DK4" t="n">
         <v>0</v>
       </c>
       <c r="DL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM4" t="n">
         <v>0</v>
@@ -2491,22 +2491,22 @@
         <v>-0</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.004829677654577759</v>
+        <v>-0.02888553057065646</v>
       </c>
       <c r="DP4" t="n">
         <v>-0</v>
       </c>
       <c r="DQ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.02383967528699446</v>
+        <v>-0.02157352108115679</v>
       </c>
       <c r="DS4" t="n">
-        <v>-0.007275649374182559</v>
+        <v>0.02176127773523201</v>
       </c>
       <c r="DT4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU4" t="n">
         <v>-0</v>
@@ -2518,115 +2518,115 @@
         <v>-0</v>
       </c>
       <c r="DX4" t="n">
-        <v>-0.03542985420251973</v>
+        <v>0.01027660164552119</v>
       </c>
       <c r="DY4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ4" t="n">
         <v>0</v>
       </c>
       <c r="EA4" t="n">
-        <v>-0.05466988484118181</v>
+        <v>-0.08039537801007207</v>
       </c>
       <c r="EB4" t="n">
-        <v>-0.01546466318729499</v>
+        <v>0.009744718095435352</v>
       </c>
       <c r="EC4" t="n">
         <v>-0</v>
       </c>
       <c r="ED4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE4" t="n">
         <v>-0</v>
       </c>
       <c r="EF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.003073570443278408</v>
+        <v>0.0001878911620556832</v>
       </c>
       <c r="EH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ4" t="n">
-        <v>-0.01777439847042175</v>
+        <v>-0.01612475868725763</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.01193365140839597</v>
+        <v>-0.007746611464762303</v>
       </c>
       <c r="EL4" t="n">
         <v>-0</v>
       </c>
       <c r="EM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN4" t="n">
         <v>-0</v>
       </c>
       <c r="EO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP4" t="n">
-        <v>-3.69924834339109e-05</v>
+        <v>-0.004404107740506818</v>
       </c>
       <c r="EQ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER4" t="n">
         <v>0</v>
       </c>
       <c r="ES4" t="n">
-        <v>-0.026096881742169</v>
+        <v>-0.08501300742185909</v>
       </c>
       <c r="ET4" t="n">
-        <v>-0.07810359549796825</v>
+        <v>-0.1191203658917378</v>
       </c>
       <c r="EU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX4" t="n">
         <v>-0</v>
       </c>
       <c r="EY4" t="n">
-        <v>0.003450210782838629</v>
+        <v>-0.04976791916913988</v>
       </c>
       <c r="EZ4" t="n">
         <v>-0</v>
       </c>
       <c r="FA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB4" t="n">
-        <v>-0.009540834134038348</v>
+        <v>-0.009153421454792306</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.03227481104388206</v>
+        <v>0.02304983545186407</v>
       </c>
       <c r="FD4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE4" t="n">
         <v>0</v>
       </c>
       <c r="FF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG4" t="n">
         <v>0</v>
       </c>
       <c r="FH4" t="n">
-        <v>-0.03316432210321903</v>
+        <v>-0.05675498652823059</v>
       </c>
       <c r="FI4" t="n">
         <v>0</v>
@@ -2635,10 +2635,10 @@
         <v>-0</v>
       </c>
       <c r="FK4" t="n">
-        <v>-0.05584644359680139</v>
+        <v>0.03185622591778713</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.003086836350783378</v>
+        <v>-0.007431153907854301</v>
       </c>
       <c r="FM4" t="n">
         <v>0</v>
@@ -2650,37 +2650,37 @@
         <v>0</v>
       </c>
       <c r="FP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ4" t="n">
-        <v>-0.006060241259846548</v>
+        <v>0.01277958116685735</v>
       </c>
       <c r="FR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS4" t="n">
         <v>-0</v>
       </c>
       <c r="FT4" t="n">
-        <v>-0.02139939197442415</v>
+        <v>0.01039118569441852</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.05505920051084613</v>
+        <v>-0.08170375329697108</v>
       </c>
       <c r="FV4" t="n">
         <v>-0</v>
       </c>
       <c r="FW4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ4" t="n">
-        <v>-0.02224577209351213</v>
+        <v>-0.0087695102032114</v>
       </c>
       <c r="GA4" t="n">
         <v>0</v>
@@ -2692,13 +2692,13 @@
         <v>-0</v>
       </c>
       <c r="GD4" t="n">
-        <v>-0.009777578274785516</v>
+        <v>-0.02395505475382675</v>
       </c>
       <c r="GE4" t="n">
         <v>0</v>
       </c>
       <c r="GF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG4" t="n">
         <v>0</v>
@@ -2709,16 +2709,16 @@
         <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.2075710264731222</v>
+        <v>0.1391254214563732</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.03590699539356513</v>
+        <v>-0.0259017384525428</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.05307922045671865</v>
+        <v>-0.03188268852774076</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -2730,22 +2730,22 @@
         <v>-0</v>
       </c>
       <c r="I5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1460866481045169</v>
+        <v>0.1348741068018432</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0.006027349692434381</v>
+        <v>0.006487348815200828</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0556006460123864</v>
+        <v>-0.042555066365535</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -2757,82 +2757,82 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.09083607563844245</v>
+        <v>0.05076860846726729</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.0159080329123034</v>
+        <v>-0.02707665960330142</v>
       </c>
       <c r="W5" t="n">
-        <v>0.00473180426870635</v>
+        <v>-0.03525792990327981</v>
       </c>
       <c r="X5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
         <v>-0</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.01853689591183033</v>
+        <v>-0.006944797372256122</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.01222797280600029</v>
+        <v>-0.01416646876437052</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.005393185036085279</v>
+        <v>-0.02707262464522101</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
         <v>-0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.05027153091867254</v>
+        <v>0.06913229683295134</v>
       </c>
       <c r="AM5" t="n">
         <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.05308372555696229</v>
+        <v>-0.02193180757752525</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.038100309085953</v>
+        <v>0.0206769023149063</v>
       </c>
       <c r="AP5" t="n">
         <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR5" t="n">
         <v>-0</v>
@@ -2844,25 +2844,25 @@
         <v>-0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.3764601081797168</v>
+        <v>0.25041048306137</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.05023759751246739</v>
+        <v>-0.08487325885660943</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.1667530853617315</v>
+        <v>-0.1189642934061028</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ5" t="n">
         <v>-0</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB5" t="n">
         <v>-0</v>
@@ -2871,16 +2871,16 @@
         <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.0001309186093275899</v>
+        <v>-0.008815963788233429</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.005667295108598497</v>
+        <v>-0.001439482947447554</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.04004872393164925</v>
+        <v>-0.006339470188831841</v>
       </c>
       <c r="BH5" t="n">
         <v>0</v>
@@ -2889,7 +2889,7 @@
         <v>-0</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK5" t="n">
         <v>0</v>
@@ -2898,22 +2898,22 @@
         <v>-0</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.01880079778794243</v>
+        <v>0.008691248367272834</v>
       </c>
       <c r="BN5" t="n">
         <v>-0</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.09033810658304926</v>
+        <v>0.03408252055101885</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.07044679191438342</v>
+        <v>0.05379683113057358</v>
       </c>
       <c r="BQ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS5" t="n">
         <v>-0</v>
@@ -2925,25 +2925,25 @@
         <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.2166695356655909</v>
+        <v>0.1800973914898893</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX5" t="n">
-        <v>-0.01884529904850071</v>
+        <v>-0.06649028178784715</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.01860954594623878</v>
+        <v>-0.02883062493055557</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA5" t="n">
         <v>-0</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC5" t="n">
         <v>0</v>
@@ -2952,103 +2952,103 @@
         <v>-0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.08142714738652627</v>
+        <v>-0.0797476264946245</v>
       </c>
       <c r="CF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.01787134975245742</v>
+        <v>0.06737239146146837</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.002875739133642849</v>
+        <v>0.01044320760185336</v>
       </c>
       <c r="CI5" t="n">
         <v>-0</v>
       </c>
       <c r="CJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK5" t="n">
         <v>0</v>
       </c>
       <c r="CL5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.0116582755103712</v>
+        <v>-0.06045594040355749</v>
       </c>
       <c r="CO5" t="n">
         <v>-0</v>
       </c>
       <c r="CP5" t="n">
-        <v>-0.0636850785394885</v>
+        <v>0.07924691439205724</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.140241436488009</v>
+        <v>0.03136390236999922</v>
       </c>
       <c r="CR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS5" t="n">
         <v>-0</v>
       </c>
       <c r="CT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV5" t="n">
         <v>0</v>
       </c>
       <c r="CW5" t="n">
-        <v>-0.06650937473073899</v>
+        <v>-0.08212957218065153</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.04952390686592778</v>
+        <v>0.07497245424655204</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.005756049570457458</v>
+        <v>0.01831961764857601</v>
       </c>
       <c r="DA5" t="n">
         <v>0</v>
       </c>
       <c r="DB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE5" t="n">
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.06401177384910922</v>
+        <v>-0.06906616328509453</v>
       </c>
       <c r="DG5" t="n">
         <v>0</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.02901871759100446</v>
+        <v>0.05180919616264787</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.0192044510068331</v>
+        <v>-0.03258065228918771</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL5" t="n">
         <v>0</v>
@@ -3060,19 +3060,19 @@
         <v>-0</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.06044326764948661</v>
+        <v>-0.04326173612650681</v>
       </c>
       <c r="DP5" t="n">
         <v>-0</v>
       </c>
       <c r="DQ5" t="n">
-        <v>-0.03714974989911334</v>
+        <v>0.02197142887469071</v>
       </c>
       <c r="DR5" t="n">
-        <v>-0.03006878493996655</v>
+        <v>-0.03466116896053003</v>
       </c>
       <c r="DS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT5" t="n">
         <v>-0</v>
@@ -3087,124 +3087,124 @@
         <v>-0</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.04954306130255846</v>
+        <v>0.03489070411825257</v>
       </c>
       <c r="DY5" t="n">
         <v>0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>-0.03004552167587464</v>
+        <v>0.03422437351935206</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0.02198507771394199</v>
+        <v>-0.02794466111967009</v>
       </c>
       <c r="EB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC5" t="n">
         <v>0</v>
       </c>
       <c r="ED5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.03704525468111271</v>
+        <v>-0.03641092045880301</v>
       </c>
       <c r="EH5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.07526832646021099</v>
+        <v>0.06163587635001496</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.04999530074896092</v>
+        <v>0.002666185944579628</v>
       </c>
       <c r="EK5" t="n">
         <v>-0</v>
       </c>
       <c r="EL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.07248629510025692</v>
+        <v>-0.04806918903970174</v>
       </c>
       <c r="EQ5" t="n">
         <v>0</v>
       </c>
       <c r="ER5" t="n">
-        <v>-0.08473461675030841</v>
+        <v>-0.05460896326348311</v>
       </c>
       <c r="ES5" t="n">
-        <v>-0.004072519219920379</v>
+        <v>-0.01273574195054598</v>
       </c>
       <c r="ET5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX5" t="n">
         <v>-0</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.0761677651166002</v>
+        <v>-0.0918792151242441</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.03928451506912989</v>
+        <v>0.07314462755193091</v>
       </c>
       <c r="FB5" t="n">
-        <v>-0.008262393310649513</v>
+        <v>0.005755353579500622</v>
       </c>
       <c r="FC5" t="n">
         <v>-0</v>
       </c>
       <c r="FD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG5" t="n">
         <v>-0</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.01035787096002788</v>
+        <v>-0.04636356749830473</v>
       </c>
       <c r="FI5" t="n">
         <v>-0</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.05758179178329179</v>
+        <v>0.02886017392394095</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.002330253095664959</v>
+        <v>0.01575059469517612</v>
       </c>
       <c r="FL5" t="n">
         <v>0</v>
@@ -3216,28 +3216,28 @@
         <v>-0</v>
       </c>
       <c r="FO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>-0.01097658537398856</v>
+        <v>0.005665270506299047</v>
       </c>
       <c r="FR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS5" t="n">
-        <v>-0.007700274590094368</v>
+        <v>0.07041300738900648</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.02651906227288799</v>
+        <v>-0.02919577736490775</v>
       </c>
       <c r="FU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW5" t="n">
         <v>0</v>
@@ -3246,31 +3246,31 @@
         <v>0</v>
       </c>
       <c r="FY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>-0.001623128403067436</v>
+        <v>-0.05264412018609505</v>
       </c>
       <c r="GA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB5" t="n">
-        <v>-0.01719467264400307</v>
+        <v>0.01257693536473105</v>
       </c>
       <c r="GC5" t="n">
         <v>0</v>
       </c>
       <c r="GD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE5" t="n">
         <v>-0</v>
       </c>
       <c r="GF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -3847,43 +3847,43 @@
         <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.1833946295121877</v>
+        <v>0.04753256310226123</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0.005566469297218501</v>
+        <v>0.00338887085367366</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.02438900821549439</v>
+        <v>-0.01470029415354531</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1074076462687437</v>
+        <v>0.05750252916615381</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.02432422288873909</v>
+        <v>0.01605838422695918</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.02409262934088309</v>
+        <v>-0.02282403140482536</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -3895,25 +3895,25 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.06709541571230969</v>
+        <v>0.02816421769637771</v>
       </c>
       <c r="U7" t="n">
         <v>-0</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.02523185312008571</v>
+        <v>-0.01640689087248993</v>
       </c>
       <c r="W7" t="n">
-        <v>0.05172611103908145</v>
+        <v>-0.009801664052594727</v>
       </c>
       <c r="X7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
         <v>-0</v>
@@ -3925,46 +3925,46 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.01371470279806811</v>
+        <v>0.0003425654316455164</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.002525980933937004</v>
+        <v>-0.009108234988328771</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.004984011743499482</v>
+        <v>-0.006057356926643521</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>-0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>-0.002723774083842524</v>
+        <v>0.0265815313059282</v>
       </c>
       <c r="AM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>-0.01445053134322827</v>
+        <v>-0.002497891805486014</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.02823828505453842</v>
+        <v>0.02669225728055598</v>
       </c>
       <c r="AP7" t="n">
         <v>0</v>
@@ -3973,25 +3973,25 @@
         <v>-0</v>
       </c>
       <c r="AR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS7" t="n">
         <v>0</v>
       </c>
       <c r="AT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.3085149523412326</v>
+        <v>0.0969789319583842</v>
       </c>
       <c r="AV7" t="n">
         <v>-0</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.03763519912356939</v>
+        <v>-0.01283798507597412</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.1035290138635785</v>
+        <v>-0.04889356971720581</v>
       </c>
       <c r="AY7" t="n">
         <v>-0</v>
@@ -4000,25 +4000,25 @@
         <v>-0</v>
       </c>
       <c r="BA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
         <v>-0</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.01219549450349634</v>
+        <v>-0.01345074906748761</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>-0.006995624913200288</v>
+        <v>-0.000279769696406516</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.0213233461018038</v>
+        <v>-0.003390378699563332</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
@@ -4027,7 +4027,7 @@
         <v>-0</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK7" t="n">
         <v>0</v>
@@ -4036,19 +4036,19 @@
         <v>-0</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.08598606153602392</v>
+        <v>0.02952731554008573</v>
       </c>
       <c r="BN7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.006113884257658905</v>
+        <v>0.008662811251435108</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.1261857093936828</v>
+        <v>0.03506487856787852</v>
       </c>
       <c r="BQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR7" t="n">
         <v>0</v>
@@ -4063,43 +4063,43 @@
         <v>-0</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.1553377606990722</v>
+        <v>0.07477612885156656</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.02257801025947553</v>
+        <v>-0.02724073581379987</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.03808649520200033</v>
+        <v>-0.01743551639558066</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA7" t="n">
         <v>-0</v>
       </c>
       <c r="CB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.06243274354151865</v>
+        <v>-0.02375997772080227</v>
       </c>
       <c r="CF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG7" t="n">
-        <v>-0.001466394750889546</v>
+        <v>0.02219712494542525</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.0002594021030163396</v>
+        <v>0.01158235289062058</v>
       </c>
       <c r="CI7" t="n">
         <v>-0</v>
@@ -4117,22 +4117,22 @@
         <v>0</v>
       </c>
       <c r="CN7" t="n">
-        <v>-0.04281599025194242</v>
+        <v>-0.03361899592311873</v>
       </c>
       <c r="CO7" t="n">
         <v>-0</v>
       </c>
       <c r="CP7" t="n">
-        <v>-0.04564960580166921</v>
+        <v>0.02656856146588677</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.07614509007848622</v>
+        <v>0.02640972219555752</v>
       </c>
       <c r="CR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT7" t="n">
         <v>-0</v>
@@ -4141,19 +4141,19 @@
         <v>-0</v>
       </c>
       <c r="CV7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.04396372480464487</v>
+        <v>-0.02509818801099282</v>
       </c>
       <c r="CX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.008191989002963434</v>
+        <v>0.02745706888054002</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.002990274087386738</v>
+        <v>0.0127813911995888</v>
       </c>
       <c r="DA7" t="n">
         <v>0</v>
@@ -4162,106 +4162,106 @@
         <v>0</v>
       </c>
       <c r="DC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD7" t="n">
         <v>0</v>
       </c>
       <c r="DE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.01523634537380298</v>
+        <v>0.002332843746416817</v>
       </c>
       <c r="DG7" t="n">
         <v>0</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.03237042917363452</v>
+        <v>0.006004629776369212</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.008433599666897716</v>
+        <v>-0.004133697898503017</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK7" t="n">
         <v>-0</v>
       </c>
       <c r="DL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>-0.07539416842133174</v>
+        <v>-0.02817577305877025</v>
       </c>
       <c r="DP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>-0.02774980358138547</v>
+        <v>-0.0196112774398961</v>
       </c>
       <c r="DR7" t="n">
-        <v>-0.008229257167387869</v>
+        <v>-0.02206953125895193</v>
       </c>
       <c r="DS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU7" t="n">
         <v>-0</v>
       </c>
       <c r="DV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW7" t="n">
         <v>-0</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.00603953326451072</v>
+        <v>0.03429636096043723</v>
       </c>
       <c r="DY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ7" t="n">
-        <v>-0.01961071981516809</v>
+        <v>0.0128495604979116</v>
       </c>
       <c r="EA7" t="n">
-        <v>-0.02944017528176902</v>
+        <v>-0.03690010413160588</v>
       </c>
       <c r="EB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC7" t="n">
         <v>0</v>
       </c>
       <c r="ED7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.03829126718823388</v>
+        <v>0.001348436116531673</v>
       </c>
       <c r="EH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.01071550745073965</v>
+        <v>0.01630451560595224</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.02682351888866063</v>
+        <v>0.02228281288819857</v>
       </c>
       <c r="EK7" t="n">
         <v>-0</v>
@@ -4270,7 +4270,7 @@
         <v>-0</v>
       </c>
       <c r="EM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN7" t="n">
         <v>-0</v>
@@ -4279,22 +4279,22 @@
         <v>0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.04692976681875548</v>
+        <v>-0.003472480288112217</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER7" t="n">
-        <v>-0.01085878475703623</v>
+        <v>0.01554717165750182</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.0257017261687748</v>
+        <v>0.008262678845101476</v>
       </c>
       <c r="ET7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV7" t="n">
         <v>-0</v>
@@ -4306,79 +4306,79 @@
         <v>0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.04729379534193819</v>
+        <v>-0.02849526878653025</v>
       </c>
       <c r="EZ7" t="n">
         <v>-0</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.002148858631404884</v>
+        <v>0.03086200295162897</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.01737643138216672</v>
+        <v>0.008397764509255844</v>
       </c>
       <c r="FC7" t="n">
         <v>-0</v>
       </c>
       <c r="FD7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF7" t="n">
         <v>-0</v>
       </c>
       <c r="FG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH7" t="n">
-        <v>0.02458726339816078</v>
+        <v>0.003246011286383898</v>
       </c>
       <c r="FI7" t="n">
         <v>-0</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.01453304255569812</v>
+        <v>0.008515660251152614</v>
       </c>
       <c r="FK7" t="n">
-        <v>-0.01140857008059026</v>
+        <v>-0.0191728122023302</v>
       </c>
       <c r="FL7" t="n">
         <v>-0</v>
       </c>
       <c r="FM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>-0.05604565431504115</v>
+        <v>0.01661513314147016</v>
       </c>
       <c r="FR7" t="n">
         <v>0</v>
       </c>
       <c r="FS7" t="n">
-        <v>-0.04036372734925222</v>
+        <v>0.03327981545545622</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.0009924990478452076</v>
+        <v>-0.04264669119975473</v>
       </c>
       <c r="FU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX7" t="n">
         <v>0</v>
@@ -4387,28 +4387,28 @@
         <v>-0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.002652260719689175</v>
+        <v>-0.00147912542622158</v>
       </c>
       <c r="GA7" t="n">
         <v>-0</v>
       </c>
       <c r="GB7" t="n">
-        <v>-0.04161401210159109</v>
+        <v>-0.001496537419251565</v>
       </c>
       <c r="GC7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF7" t="n">
         <v>0</v>
       </c>
       <c r="GG7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -4416,22 +4416,22 @@
         <v>0</v>
       </c>
       <c r="B8" t="n">
-        <v>0.2069018907631628</v>
+        <v>0.1196863132968252</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.00846111527722331</v>
+        <v>-0.01645140739886982</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1119112871933143</v>
+        <v>-0.04160659223066263</v>
       </c>
       <c r="G8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>-0</v>
@@ -4443,25 +4443,25 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1517345421512717</v>
+        <v>0.1674378998764142</v>
       </c>
       <c r="L8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.006474037752332974</v>
+        <v>-0.04397912831012565</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.08383314009128601</v>
+        <v>-0.02384512266645554</v>
       </c>
       <c r="P8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -4470,34 +4470,34 @@
         <v>-0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.006802304868708245</v>
+        <v>0.03258737214747885</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.06028840373102225</v>
+        <v>-0.02650327321563277</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.01773852806391406</v>
+        <v>-0.004657445385262957</v>
       </c>
       <c r="Y8" t="n">
         <v>-0</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.01769578407517146</v>
+        <v>-0.006005458023294039</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
@@ -4506,25 +4506,25 @@
         <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.008520869361489184</v>
+        <v>-0.02026365014759193</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.0005002243809105897</v>
+        <v>0.0005743458858178894</v>
       </c>
       <c r="AH8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>-0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK8" t="n">
         <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.02299301606004735</v>
+        <v>0.03424606479776449</v>
       </c>
       <c r="AM8" t="n">
         <v>0</v>
@@ -4533,13 +4533,13 @@
         <v>0</v>
       </c>
       <c r="AO8" t="n">
-        <v>-0.02685920507965994</v>
+        <v>0.01304457596774273</v>
       </c>
       <c r="AP8" t="n">
-        <v>-0.06510924328586748</v>
+        <v>-0.01943323859730163</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR8" t="n">
         <v>-0</v>
@@ -4548,28 +4548,28 @@
         <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.2539454654402311</v>
+        <v>0.1887373153978018</v>
       </c>
       <c r="AV8" t="n">
         <v>-0</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX8" t="n">
-        <v>-0.002514165660445164</v>
+        <v>-0.06421559649558288</v>
       </c>
       <c r="AY8" t="n">
-        <v>-0.1181198935842529</v>
+        <v>-0.05143045685553306</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB8" t="n">
         <v>0</v>
@@ -4578,7 +4578,7 @@
         <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.04308295281005821</v>
+        <v>-0.004020451930252605</v>
       </c>
       <c r="BE8" t="n">
         <v>0</v>
@@ -4587,64 +4587,64 @@
         <v>0</v>
       </c>
       <c r="BG8" t="n">
-        <v>-0.01814301357328646</v>
+        <v>-0.01739229111083925</v>
       </c>
       <c r="BH8" t="n">
-        <v>-0.01963445471418255</v>
+        <v>-0.01011069775623395</v>
       </c>
       <c r="BI8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.1086783507844073</v>
+        <v>-0.002991507311257718</v>
       </c>
       <c r="BN8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO8" t="n">
         <v>-0</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.04859738889482534</v>
+        <v>0.04839411629070341</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.01451807723146773</v>
+        <v>0.006729537612690376</v>
       </c>
       <c r="BR8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.1154623558464437</v>
+        <v>0.1383506487028203</v>
       </c>
       <c r="BW8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX8" t="n">
         <v>0</v>
       </c>
       <c r="BY8" t="n">
-        <v>-0.02513225869129944</v>
+        <v>-0.01385293075634426</v>
       </c>
       <c r="BZ8" t="n">
-        <v>-0.008975248084310963</v>
+        <v>-0.03475321486331361</v>
       </c>
       <c r="CA8" t="n">
         <v>-0</v>
@@ -4659,46 +4659,46 @@
         <v>-0</v>
       </c>
       <c r="CE8" t="n">
-        <v>-0.05645423365698907</v>
+        <v>-0.06997469010771623</v>
       </c>
       <c r="CF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG8" t="n">
         <v>-0</v>
       </c>
       <c r="CH8" t="n">
-        <v>-0.01613835826883399</v>
+        <v>0.007881875277849794</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.04589253727423845</v>
+        <v>0.03889240972388695</v>
       </c>
       <c r="CJ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN8" t="n">
-        <v>-0.01777405624972949</v>
+        <v>-0.09042199098968229</v>
       </c>
       <c r="CO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.01973892415822712</v>
+        <v>0.05231216585725638</v>
       </c>
       <c r="CR8" t="n">
-        <v>-0.06600801573134046</v>
+        <v>0.05226919133950762</v>
       </c>
       <c r="CS8" t="n">
         <v>-0</v>
@@ -4707,31 +4707,31 @@
         <v>-0</v>
       </c>
       <c r="CU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV8" t="n">
         <v>0</v>
       </c>
       <c r="CW8" t="n">
-        <v>-0.03833984870147673</v>
+        <v>-0.06492773735246292</v>
       </c>
       <c r="CX8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY8" t="n">
         <v>0</v>
       </c>
       <c r="CZ8" t="n">
-        <v>-0.0156949134120486</v>
+        <v>0.00419778331380426</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.04856156451374286</v>
+        <v>0.0409641534527774</v>
       </c>
       <c r="DB8" t="n">
         <v>0</v>
       </c>
       <c r="DC8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD8" t="n">
         <v>0</v>
@@ -4740,19 +4740,19 @@
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>-0.00586374944524602</v>
+        <v>-0.01052878804070651</v>
       </c>
       <c r="DG8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.003515623722707651</v>
+        <v>-0.01653149178568806</v>
       </c>
       <c r="DJ8" t="n">
-        <v>-0.0009184311241464639</v>
+        <v>0.01630400976577785</v>
       </c>
       <c r="DK8" t="n">
         <v>0</v>
@@ -4767,49 +4767,49 @@
         <v>-0</v>
       </c>
       <c r="DO8" t="n">
-        <v>-0.02663759557159015</v>
+        <v>-0.03412272417801981</v>
       </c>
       <c r="DP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ8" t="n">
         <v>0</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.04150585139098215</v>
+        <v>0.02433696367840378</v>
       </c>
       <c r="DS8" t="n">
-        <v>-0.02161104935025494</v>
+        <v>-0.008909963277296887</v>
       </c>
       <c r="DT8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU8" t="n">
         <v>-0</v>
       </c>
       <c r="DV8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW8" t="n">
         <v>-0</v>
       </c>
       <c r="DX8" t="n">
-        <v>-0.02780643515945038</v>
+        <v>0.04344456035234161</v>
       </c>
       <c r="DY8" t="n">
         <v>0</v>
       </c>
       <c r="DZ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA8" t="n">
-        <v>-0.03227693880653135</v>
+        <v>0.008094711978906512</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.008615440702362103</v>
+        <v>-0.07289264839059334</v>
       </c>
       <c r="EC8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED8" t="n">
         <v>0</v>
@@ -4821,7 +4821,7 @@
         <v>-0</v>
       </c>
       <c r="EG8" t="n">
-        <v>-0.02536614365682714</v>
+        <v>-0.01305583413142138</v>
       </c>
       <c r="EH8" t="n">
         <v>0</v>
@@ -4830,43 +4830,43 @@
         <v>0</v>
       </c>
       <c r="EJ8" t="n">
-        <v>-0.002206088737139606</v>
+        <v>-0.01335335407121339</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.03738933611054709</v>
+        <v>0.02111697090267368</v>
       </c>
       <c r="EL8" t="n">
         <v>-0</v>
       </c>
       <c r="EM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP8" t="n">
-        <v>-0.04958561660892619</v>
+        <v>-0.02708217275619721</v>
       </c>
       <c r="EQ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES8" t="n">
-        <v>-0.03318980148801932</v>
+        <v>-0.03726916332762593</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.0914668646435659</v>
+        <v>0.03689657664900587</v>
       </c>
       <c r="EU8" t="n">
         <v>-0</v>
       </c>
       <c r="EV8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW8" t="n">
         <v>0</v>
@@ -4875,34 +4875,34 @@
         <v>-0</v>
       </c>
       <c r="EY8" t="n">
-        <v>-0.03818176920043462</v>
+        <v>-0.07336184054501386</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA8" t="n">
         <v>-0</v>
       </c>
       <c r="FB8" t="n">
-        <v>-0.01109298072777427</v>
+        <v>-0.003744085874525529</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.04776618329130222</v>
+        <v>0.034764308888656</v>
       </c>
       <c r="FD8" t="n">
         <v>-0</v>
       </c>
       <c r="FE8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG8" t="n">
         <v>0</v>
       </c>
       <c r="FH8" t="n">
-        <v>-0.02073154695461193</v>
+        <v>-0.04699193596100097</v>
       </c>
       <c r="FI8" t="n">
         <v>-0</v>
@@ -4911,37 +4911,37 @@
         <v>-0</v>
       </c>
       <c r="FK8" t="n">
-        <v>-0.04442284622029099</v>
+        <v>0.0188218655695386</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.02209757691457121</v>
+        <v>0.008023884121732883</v>
       </c>
       <c r="FM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ8" t="n">
-        <v>-0.02983891033834852</v>
+        <v>0.003912257216902021</v>
       </c>
       <c r="FR8" t="n">
         <v>-0</v>
       </c>
       <c r="FS8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FT8" t="n">
-        <v>-0.02314034242062989</v>
+        <v>-0.0009236514192508121</v>
       </c>
       <c r="FU8" t="n">
-        <v>0.004158234495905312</v>
+        <v>-0.001222645870382971</v>
       </c>
       <c r="FV8" t="n">
         <v>-0</v>
@@ -4950,16 +4950,16 @@
         <v>-0</v>
       </c>
       <c r="FX8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ8" t="n">
-        <v>-0.0370889267041082</v>
+        <v>-0.02574636830648108</v>
       </c>
       <c r="GA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB8" t="n">
         <v>-0</v>
@@ -4968,13 +4968,13 @@
         <v>0</v>
       </c>
       <c r="GD8" t="n">
-        <v>-0.03622604401714288</v>
+        <v>0.01089963644522911</v>
       </c>
       <c r="GE8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG8" t="n">
         <v>0</v>
@@ -4988,94 +4988,94 @@
         <v>-0</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.2466195138335361</v>
+        <v>-0.03501925634010804</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3243404453774759</v>
+        <v>0.01800375358518042</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.04981240183347063</v>
+        <v>-0.03933341877379692</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.2023130499497898</v>
+        <v>-0.0255490698140824</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3582656316996748</v>
+        <v>0.01287628394532755</v>
       </c>
       <c r="N9" t="n">
-        <v>0.07459443337571414</v>
+        <v>-0.03860446815715828</v>
       </c>
       <c r="O9" t="n">
         <v>-0</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1249784074463029</v>
+        <v>-0.004592362066178358</v>
       </c>
       <c r="V9" t="n">
-        <v>0.1201695343183933</v>
+        <v>0.02382342674545925</v>
       </c>
       <c r="W9" t="n">
-        <v>0.01023802438104036</v>
+        <v>0.002789831478353648</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z9" t="n">
         <v>-0</v>
       </c>
       <c r="AA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AD9" t="n">
-        <v>-0.007742859899154958</v>
+        <v>-0.01071754885748343</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.03479452578414075</v>
+        <v>-0.01553131202261122</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.02888884096493791</v>
+        <v>-0.01466183360561034</v>
       </c>
       <c r="AG9" t="n">
         <v>-0</v>
@@ -5090,46 +5090,46 @@
         <v>-0</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AM9" t="n">
-        <v>-0.03206676815937957</v>
+        <v>-0.03609536792323536</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.03918327090780654</v>
+        <v>0.01732629523099783</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.07490686332606245</v>
+        <v>1.996311246048476e-05</v>
       </c>
       <c r="AP9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AV9" t="n">
-        <v>-0.2577630842692901</v>
+        <v>-0.06503289643253408</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.2927384772340825</v>
+        <v>0.09379113467420325</v>
       </c>
       <c r="AX9" t="n">
-        <v>-0.1873520287957601</v>
+        <v>-0.0851697762059337</v>
       </c>
       <c r="AY9" t="n">
         <v>0</v>
@@ -5150,13 +5150,13 @@
         <v>-0</v>
       </c>
       <c r="BE9" t="n">
-        <v>-0.0422092665793021</v>
+        <v>0.0004219633238163101</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.02035950308767955</v>
+        <v>-0.04820562743654833</v>
       </c>
       <c r="BG9" t="n">
-        <v>-0.0324448147954937</v>
+        <v>-0.02146107917417338</v>
       </c>
       <c r="BH9" t="n">
         <v>-0</v>
@@ -5165,25 +5165,25 @@
         <v>0</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK9" t="n">
         <v>-0</v>
       </c>
       <c r="BL9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.0574287175576622</v>
+        <v>0.01678523395424397</v>
       </c>
       <c r="BO9" t="n">
-        <v>-0.03497824345148524</v>
+        <v>0.04820706091519253</v>
       </c>
       <c r="BP9" t="n">
-        <v>-0.2012739348256257</v>
+        <v>0.06773018991386742</v>
       </c>
       <c r="BQ9" t="n">
         <v>0</v>
@@ -5192,25 +5192,25 @@
         <v>-0</v>
       </c>
       <c r="BS9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BW9" t="n">
-        <v>-0.2023999525929974</v>
+        <v>-0.03312656500566592</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.2195302516329571</v>
+        <v>0.09524523051610673</v>
       </c>
       <c r="BY9" t="n">
-        <v>-0.1535205402571478</v>
+        <v>-0.01441678493851113</v>
       </c>
       <c r="BZ9" t="n">
         <v>0</v>
@@ -5219,109 +5219,109 @@
         <v>-0</v>
       </c>
       <c r="CB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE9" t="n">
         <v>0</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.09624529553890135</v>
+        <v>0.02625963520467488</v>
       </c>
       <c r="CG9" t="n">
-        <v>-0.101263720811146</v>
+        <v>0.006824115766720362</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.000688012912228317</v>
+        <v>0.009419751572682402</v>
       </c>
       <c r="CI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL9" t="n">
         <v>0</v>
       </c>
       <c r="CM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CO9" t="n">
-        <v>0.007306869267873093</v>
+        <v>0.0131731937785592</v>
       </c>
       <c r="CP9" t="n">
-        <v>0.06430169516620289</v>
+        <v>0.02198228834203504</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.1897669432389691</v>
+        <v>0.06081173873206057</v>
       </c>
       <c r="CR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CV9" t="n">
         <v>-0</v>
       </c>
       <c r="CW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CX9" t="n">
-        <v>0.07052334102714125</v>
+        <v>0.01820116089241361</v>
       </c>
       <c r="CY9" t="n">
-        <v>-0.1003816545508291</v>
+        <v>0.003998708282726592</v>
       </c>
       <c r="CZ9" t="n">
-        <v>-0.01465126283591861</v>
+        <v>0.02039345318727289</v>
       </c>
       <c r="DA9" t="n">
         <v>0</v>
       </c>
       <c r="DB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC9" t="n">
         <v>-0</v>
       </c>
       <c r="DD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE9" t="n">
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DG9" t="n">
-        <v>-0.0002319224113602631</v>
+        <v>0.01170943007901689</v>
       </c>
       <c r="DH9" t="n">
-        <v>-0.101610502813881</v>
+        <v>-0.02114500349162779</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.002839032978573883</v>
+        <v>-0.002043092007074436</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK9" t="n">
         <v>0</v>
@@ -5330,22 +5330,22 @@
         <v>-0</v>
       </c>
       <c r="DM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO9" t="n">
         <v>0</v>
       </c>
       <c r="DP9" t="n">
-        <v>0.06968678696049138</v>
+        <v>0.008465635657623887</v>
       </c>
       <c r="DQ9" t="n">
-        <v>-0.05370606041233692</v>
+        <v>-0.007556972077097038</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.1770716512929111</v>
+        <v>0.04192039288441478</v>
       </c>
       <c r="DS9" t="n">
         <v>-0</v>
@@ -5354,160 +5354,160 @@
         <v>-0</v>
       </c>
       <c r="DU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DY9" t="n">
-        <v>0.01897966457105051</v>
+        <v>-0.03293338305683217</v>
       </c>
       <c r="DZ9" t="n">
-        <v>0.0619283952196745</v>
+        <v>-0.01947363234344802</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.08208374700809655</v>
+        <v>-0.03229592638590866</v>
       </c>
       <c r="EB9" t="n">
         <v>-0</v>
       </c>
       <c r="EC9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EH9" t="n">
-        <v>0.1070296818220138</v>
+        <v>-0.002424352845907031</v>
       </c>
       <c r="EI9" t="n">
-        <v>-0.1481072434798718</v>
+        <v>0.01488652497050834</v>
       </c>
       <c r="EJ9" t="n">
-        <v>-0.05657143041760419</v>
+        <v>-0.003055838880456945</v>
       </c>
       <c r="EK9" t="n">
         <v>0</v>
       </c>
       <c r="EL9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM9" t="n">
         <v>0</v>
       </c>
       <c r="EN9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0.04391844441453417</v>
+        <v>-0.005091996649096789</v>
       </c>
       <c r="ER9" t="n">
-        <v>-0.06168010185343836</v>
+        <v>-0.02007039546526832</v>
       </c>
       <c r="ES9" t="n">
-        <v>-0.01626281968545122</v>
+        <v>0.01218194936965704</v>
       </c>
       <c r="ET9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW9" t="n">
         <v>-0</v>
       </c>
       <c r="EX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EZ9" t="n">
-        <v>0.08558940545103037</v>
+        <v>0.01884920957254008</v>
       </c>
       <c r="FA9" t="n">
-        <v>-0.1034158297091191</v>
+        <v>-0.004700499520995619</v>
       </c>
       <c r="FB9" t="n">
-        <v>-0.0199851425889862</v>
+        <v>0.01411821091277532</v>
       </c>
       <c r="FC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FI9" t="n">
-        <v>0.04926006131606438</v>
+        <v>0.01661168966920384</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.05157663093468879</v>
+        <v>-0.002685157621702132</v>
       </c>
       <c r="FK9" t="n">
-        <v>-0.08544278665225338</v>
+        <v>-0.04238382091309489</v>
       </c>
       <c r="FL9" t="n">
         <v>0</v>
       </c>
       <c r="FM9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO9" t="n">
         <v>0</v>
       </c>
       <c r="FP9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FR9" t="n">
-        <v>0.009222983975186968</v>
+        <v>3.934788834994866e-05</v>
       </c>
       <c r="FS9" t="n">
-        <v>-0.0004822645837708803</v>
+        <v>0.003392978466042412</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.03692226882798856</v>
+        <v>0.05132137987282395</v>
       </c>
       <c r="FU9" t="n">
         <v>-0</v>
@@ -5516,10 +5516,10 @@
         <v>0</v>
       </c>
       <c r="FW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY9" t="n">
         <v>-0</v>
@@ -5528,10 +5528,10 @@
         <v>0</v>
       </c>
       <c r="GA9" t="n">
-        <v>-0.01351598292434609</v>
+        <v>0.01155073262297827</v>
       </c>
       <c r="GB9" t="n">
-        <v>0.05035447284895019</v>
+        <v>-0.02927161626445916</v>
       </c>
       <c r="GC9" t="n">
         <v>0</v>
@@ -5540,13 +5540,13 @@
         <v>0</v>
       </c>
       <c r="GE9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="10">
@@ -6123,7 +6123,7 @@
         <v>0</v>
       </c>
       <c r="B11" t="n">
-        <v>0.1631647665904847</v>
+        <v>0.2503941783463266</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -6132,10 +6132,10 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.06391955612678862</v>
+        <v>0.04354074010111095</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.07229919706120887</v>
+        <v>-0.1082474882554239</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -6150,7 +6150,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1229319883679403</v>
+        <v>0.3529543536091608</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -6159,16 +6159,16 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0688673436687537</v>
+        <v>-0.008069257480609621</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.08956092418019262</v>
+        <v>-0.1182442737698028</v>
       </c>
       <c r="P11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -6177,7 +6177,7 @@
         <v>-0</v>
       </c>
       <c r="T11" t="n">
-        <v>0.03085017927883478</v>
+        <v>0.08839682388704319</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -6186,37 +6186,37 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.01472065673683478</v>
+        <v>-0.09721137553492774</v>
       </c>
       <c r="X11" t="n">
-        <v>0.02827176891571712</v>
+        <v>0.02336715599341926</v>
       </c>
       <c r="Y11" t="n">
         <v>-0</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB11" t="n">
         <v>-0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.01910680888366231</v>
+        <v>-0.0118336027358107</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.01599645473001217</v>
+        <v>-0.08014546506662854</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.008803264459871904</v>
+        <v>-0.02134443458232521</v>
       </c>
       <c r="AH11" t="n">
         <v>-0</v>
@@ -6225,13 +6225,13 @@
         <v>-0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK11" t="n">
         <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.0295362588118875</v>
+        <v>0.05366361774645988</v>
       </c>
       <c r="AM11" t="n">
         <v>0</v>
@@ -6240,25 +6240,25 @@
         <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>-0.008741478561553134</v>
+        <v>-0.01138303085387012</v>
       </c>
       <c r="AP11" t="n">
-        <v>-0.0227855623595465</v>
+        <v>-0.05286937764898148</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR11" t="n">
         <v>-0</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.1637317042349686</v>
+        <v>0.3857018776480945</v>
       </c>
       <c r="AV11" t="n">
         <v>0</v>
@@ -6267,25 +6267,25 @@
         <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>-0.04692470472254477</v>
+        <v>-0.1736593883816442</v>
       </c>
       <c r="AY11" t="n">
-        <v>-0.03297330314988988</v>
+        <v>-0.06661615531932497</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC11" t="n">
         <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.03495862464794177</v>
+        <v>-0.01736416592631222</v>
       </c>
       <c r="BE11" t="n">
         <v>0</v>
@@ -6294,52 +6294,52 @@
         <v>0</v>
       </c>
       <c r="BG11" t="n">
-        <v>-0.03310904215502401</v>
+        <v>-0.01735183111911656</v>
       </c>
       <c r="BH11" t="n">
-        <v>-0.03224179484706267</v>
+        <v>-0.06638808952646492</v>
       </c>
       <c r="BI11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK11" t="n">
         <v>0</v>
       </c>
       <c r="BL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.05858378329402152</v>
+        <v>0.06858799061032202</v>
       </c>
       <c r="BN11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO11" t="n">
         <v>-0</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.02497356370197956</v>
+        <v>0.0614838581771348</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.01585611067743616</v>
+        <v>0.01099700222375083</v>
       </c>
       <c r="BR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS11" t="n">
         <v>0</v>
       </c>
       <c r="BT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU11" t="n">
         <v>-0</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.08284185229585676</v>
+        <v>0.2701075878710738</v>
       </c>
       <c r="BW11" t="n">
         <v>0</v>
@@ -6348,64 +6348,64 @@
         <v>0</v>
       </c>
       <c r="BY11" t="n">
-        <v>-0.02133817773459577</v>
+        <v>-0.05799450624704959</v>
       </c>
       <c r="BZ11" t="n">
-        <v>-0.001673082981082708</v>
+        <v>-0.07283926933109415</v>
       </c>
       <c r="CA11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD11" t="n">
         <v>-0</v>
       </c>
       <c r="CE11" t="n">
-        <v>-0.03432822934518674</v>
+        <v>-0.09923716279639741</v>
       </c>
       <c r="CF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG11" t="n">
         <v>-0</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.007743387215515145</v>
+        <v>-0.01498331795866485</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.02604422156461737</v>
+        <v>0.05404509138461135</v>
       </c>
       <c r="CJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK11" t="n">
         <v>0</v>
       </c>
       <c r="CL11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM11" t="n">
         <v>0</v>
       </c>
       <c r="CN11" t="n">
-        <v>-0.01160248985606199</v>
+        <v>-0.1747925475302224</v>
       </c>
       <c r="CO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP11" t="n">
         <v>-0</v>
       </c>
       <c r="CQ11" t="n">
-        <v>-0.01127927037860827</v>
+        <v>0.1150243244126416</v>
       </c>
       <c r="CR11" t="n">
-        <v>-0.0211915640814</v>
+        <v>0.05594853271690287</v>
       </c>
       <c r="CS11" t="n">
         <v>-0</v>
@@ -6417,22 +6417,22 @@
         <v>0</v>
       </c>
       <c r="CV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW11" t="n">
-        <v>-0.02409424917833743</v>
+        <v>-0.08837129970834574</v>
       </c>
       <c r="CX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY11" t="n">
         <v>0</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.006444913274716415</v>
+        <v>-0.03497729795452542</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.03037273718030556</v>
+        <v>0.05743884439276268</v>
       </c>
       <c r="DB11" t="n">
         <v>0</v>
@@ -6447,19 +6447,19 @@
         <v>0</v>
       </c>
       <c r="DF11" t="n">
-        <v>-0.0227175805915859</v>
+        <v>-0.03663484482384912</v>
       </c>
       <c r="DG11" t="n">
         <v>-0</v>
       </c>
       <c r="DH11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.01559624673278798</v>
+        <v>-0.07954117362766847</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.0002377831611200522</v>
+        <v>-0.01404486022950918</v>
       </c>
       <c r="DK11" t="n">
         <v>0</v>
@@ -6468,136 +6468,136 @@
         <v>-0</v>
       </c>
       <c r="DM11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO11" t="n">
-        <v>-0.02876728594099061</v>
+        <v>-0.05061302566384042</v>
       </c>
       <c r="DP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.01346986028385335</v>
+        <v>-0.04650249378280968</v>
       </c>
       <c r="DS11" t="n">
-        <v>-0.02943086953714817</v>
+        <v>0.003428958390357815</v>
       </c>
       <c r="DT11" t="n">
         <v>-0</v>
       </c>
       <c r="DU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW11" t="n">
         <v>-0</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.0001835880134842231</v>
+        <v>0.05706588383190388</v>
       </c>
       <c r="DY11" t="n">
         <v>0</v>
       </c>
       <c r="DZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA11" t="n">
-        <v>-0.03380538178445851</v>
+        <v>-0.01058164990318528</v>
       </c>
       <c r="EB11" t="n">
-        <v>-0.02576819651894077</v>
+        <v>0.01933904310505061</v>
       </c>
       <c r="EC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE11" t="n">
         <v>-0</v>
       </c>
       <c r="EF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG11" t="n">
-        <v>-0.01637300649116799</v>
+        <v>-0.002541899292217534</v>
       </c>
       <c r="EH11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.01037977691949395</v>
+        <v>-0.07562148745632045</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.01531445082098795</v>
+        <v>0.01860685305002844</v>
       </c>
       <c r="EL11" t="n">
         <v>-0</v>
       </c>
       <c r="EM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN11" t="n">
         <v>-0</v>
       </c>
       <c r="EO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP11" t="n">
-        <v>-0.001224481512101909</v>
+        <v>-0.01111399727417037</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES11" t="n">
-        <v>-0.005831190921370887</v>
+        <v>-0.09730490982256185</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.03277357376775199</v>
+        <v>0.04131880369840913</v>
       </c>
       <c r="EU11" t="n">
         <v>-0</v>
       </c>
       <c r="EV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX11" t="n">
         <v>-0</v>
       </c>
       <c r="EY11" t="n">
-        <v>-0.0219504212851367</v>
+        <v>-0.110715121525507</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA11" t="n">
         <v>-0</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.004160083444604979</v>
+        <v>-0.03415898260129065</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.03120390079166824</v>
+        <v>0.04255460666031068</v>
       </c>
       <c r="FD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE11" t="n">
         <v>0</v>
@@ -6609,34 +6609,34 @@
         <v>0</v>
       </c>
       <c r="FH11" t="n">
-        <v>-0.02220199678850348</v>
+        <v>-0.09915570728337468</v>
       </c>
       <c r="FI11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ11" t="n">
         <v>-0</v>
       </c>
       <c r="FK11" t="n">
-        <v>-0.0316525883977584</v>
+        <v>0.09073672026253761</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.02817178967442036</v>
+        <v>0.0678533348717113</v>
       </c>
       <c r="FM11" t="n">
         <v>0</v>
       </c>
       <c r="FN11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO11" t="n">
         <v>0</v>
       </c>
       <c r="FP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ11" t="n">
-        <v>0.003476983436792133</v>
+        <v>0.02568119386667738</v>
       </c>
       <c r="FR11" t="n">
         <v>-0</v>
@@ -6645,25 +6645,25 @@
         <v>-0</v>
       </c>
       <c r="FT11" t="n">
-        <v>-0.00265720568882114</v>
+        <v>-0.02385849125205413</v>
       </c>
       <c r="FU11" t="n">
-        <v>0.01584344162184426</v>
+        <v>0.025872845560229</v>
       </c>
       <c r="FV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ11" t="n">
-        <v>-0.02510835057899517</v>
+        <v>-0.06237675215901579</v>
       </c>
       <c r="GA11" t="n">
         <v>0</v>
@@ -6672,10 +6672,10 @@
         <v>-0</v>
       </c>
       <c r="GC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD11" t="n">
-        <v>-0.02670685756400928</v>
+        <v>0.01493994779915329</v>
       </c>
       <c r="GE11" t="n">
         <v>-0</v>
@@ -6692,22 +6692,22 @@
         <v>0</v>
       </c>
       <c r="B12" t="n">
-        <v>0.3704374146626959</v>
+        <v>0.3479741288887487</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1325656892456129</v>
+        <v>-0.1696448212608979</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.08406689850322684</v>
+        <v>0.007422733024831339</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H12" t="n">
         <v>-0</v>
@@ -6719,22 +6719,22 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.3312435759840816</v>
+        <v>0.402055872110907</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.1577264601226698</v>
+        <v>-0.2198310073558277</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.09698927879587228</v>
+        <v>-0.03295056527008668</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -6743,22 +6743,22 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1060840700601797</v>
+        <v>0.09418859851524387</v>
       </c>
       <c r="U12" t="n">
         <v>-0</v>
       </c>
       <c r="V12" t="n">
-        <v>0.02484271692020786</v>
+        <v>-0.03505591052191264</v>
       </c>
       <c r="W12" t="n">
-        <v>0.09630361539358594</v>
+        <v>-0.07800744392685759</v>
       </c>
       <c r="X12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
         <v>-0</v>
@@ -6770,25 +6770,25 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.08489382138330921</v>
+        <v>-0.06028107700541258</v>
       </c>
       <c r="AD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.0007891451134964869</v>
+        <v>-0.07324541058189296</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.02339486985196014</v>
+        <v>-0.04094677599192958</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>-0</v>
@@ -6800,22 +6800,22 @@
         <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.02809083177280921</v>
+        <v>0.1032492630757987</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN12" t="n">
-        <v>-0.02665495256307511</v>
+        <v>-0.05072342811745973</v>
       </c>
       <c r="AO12" t="n">
-        <v>-0.01731691926107942</v>
+        <v>0.04955113812210116</v>
       </c>
       <c r="AP12" t="n">
         <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR12" t="n">
         <v>-0</v>
@@ -6824,19 +6824,19 @@
         <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.3745400484962448</v>
+        <v>0.3370938859734188</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.02187135490255947</v>
+        <v>-0.09211114922261067</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.1362720614754538</v>
+        <v>-0.1304331652270187</v>
       </c>
       <c r="AY12" t="n">
         <v>-0</v>
@@ -6845,7 +6845,7 @@
         <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
         <v>-0</v>
@@ -6854,16 +6854,16 @@
         <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.02493378707251354</v>
+        <v>-0.01821697253695006</v>
       </c>
       <c r="BE12" t="n">
         <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>-0.05184454656788751</v>
+        <v>-0.04325061148896341</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.1333488129099054</v>
+        <v>-0.0107015151090394</v>
       </c>
       <c r="BH12" t="n">
         <v>0</v>
@@ -6872,7 +6872,7 @@
         <v>-0</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK12" t="n">
         <v>0</v>
@@ -6881,22 +6881,22 @@
         <v>-0</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.0327582035420233</v>
+        <v>-0.03994509482066016</v>
       </c>
       <c r="BN12" t="n">
         <v>-0</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.05051493814437289</v>
+        <v>0.005149826395470168</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.04591837229400588</v>
+        <v>0.03345999405097997</v>
       </c>
       <c r="BQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS12" t="n">
         <v>-0</v>
@@ -6908,25 +6908,25 @@
         <v>-0</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.2296578917775768</v>
+        <v>0.2940625187048709</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>-0.005558523577686346</v>
+        <v>-0.1195943234820088</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.1019054675681897</v>
+        <v>-0.04088904000097972</v>
       </c>
       <c r="BZ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC12" t="n">
         <v>0</v>
@@ -6935,46 +6935,46 @@
         <v>-0</v>
       </c>
       <c r="CE12" t="n">
-        <v>-0.0856131203543348</v>
+        <v>-0.129709417096469</v>
       </c>
       <c r="CF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.01589315708408767</v>
+        <v>0.1203124933383748</v>
       </c>
       <c r="CH12" t="n">
-        <v>-0.02203801830188592</v>
+        <v>-0.0170826617649228</v>
       </c>
       <c r="CI12" t="n">
         <v>0</v>
       </c>
       <c r="CJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK12" t="n">
         <v>0</v>
       </c>
       <c r="CL12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM12" t="n">
         <v>0</v>
       </c>
       <c r="CN12" t="n">
-        <v>-0.02717769805245196</v>
+        <v>-0.1127362921866758</v>
       </c>
       <c r="CO12" t="n">
         <v>-0</v>
       </c>
       <c r="CP12" t="n">
-        <v>-0.09797609986093193</v>
+        <v>0.2140268737609498</v>
       </c>
       <c r="CQ12" t="n">
-        <v>-0.1789496345537216</v>
+        <v>0.0482084108439672</v>
       </c>
       <c r="CR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS12" t="n">
         <v>-0</v>
@@ -6989,22 +6989,22 @@
         <v>0</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0.07325666961957555</v>
+        <v>-0.1212948017396682</v>
       </c>
       <c r="CX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.02408575687610849</v>
+        <v>0.1228461948194744</v>
       </c>
       <c r="CZ12" t="n">
-        <v>-0.02040785673892387</v>
+        <v>-0.006898683844696632</v>
       </c>
       <c r="DA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC12" t="n">
         <v>-0</v>
@@ -7016,19 +7016,19 @@
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>-0.05783474683543961</v>
+        <v>-0.08334857864803505</v>
       </c>
       <c r="DG12" t="n">
         <v>-0</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.01762003702500684</v>
+        <v>0.01558245625648095</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.04089680043844922</v>
+        <v>-0.05801086446657901</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK12" t="n">
         <v>-0</v>
@@ -7040,22 +7040,22 @@
         <v>0</v>
       </c>
       <c r="DN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO12" t="n">
-        <v>-0.05402483479296312</v>
+        <v>-0.07533902880545749</v>
       </c>
       <c r="DP12" t="n">
         <v>-0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>-0.036646247567667</v>
+        <v>0.09382575748529619</v>
       </c>
       <c r="DR12" t="n">
-        <v>-0.092020115626101</v>
+        <v>-0.01266955700555564</v>
       </c>
       <c r="DS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT12" t="n">
         <v>-0</v>
@@ -7067,79 +7067,79 @@
         <v>0</v>
       </c>
       <c r="DW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.06009164183283167</v>
+        <v>0.02600821269405029</v>
       </c>
       <c r="DY12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ12" t="n">
-        <v>-0.02193519080440557</v>
+        <v>-0.05629514531041691</v>
       </c>
       <c r="EA12" t="n">
-        <v>-0.03582904766905046</v>
+        <v>0.04226624076027799</v>
       </c>
       <c r="EB12" t="n">
         <v>0</v>
       </c>
       <c r="EC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE12" t="n">
         <v>-0</v>
       </c>
       <c r="EF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG12" t="n">
-        <v>-0.05427007372179741</v>
+        <v>-0.08740562310917169</v>
       </c>
       <c r="EH12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.03767771483853015</v>
+        <v>0.07117836963366761</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.04896083106870074</v>
+        <v>0.01452364106939523</v>
       </c>
       <c r="EK12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN12" t="n">
         <v>-0</v>
       </c>
       <c r="EO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP12" t="n">
-        <v>-0.05782315622065556</v>
+        <v>-0.06306510257113387</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.008890265118134554</v>
+        <v>0.04691124939377768</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.01813200861346611</v>
+        <v>-0.02642548816736122</v>
       </c>
       <c r="ET12" t="n">
         <v>-0</v>
       </c>
       <c r="EU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV12" t="n">
         <v>0</v>
@@ -7148,46 +7148,46 @@
         <v>-0</v>
       </c>
       <c r="EX12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY12" t="n">
-        <v>-0.08427181449230588</v>
+        <v>-0.1383018233718567</v>
       </c>
       <c r="EZ12" t="n">
         <v>-0</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.03472361415519355</v>
+        <v>0.1262469586144748</v>
       </c>
       <c r="FB12" t="n">
-        <v>-0.02536164537894336</v>
+        <v>-0.01930401991991051</v>
       </c>
       <c r="FC12" t="n">
         <v>-0</v>
       </c>
       <c r="FD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE12" t="n">
         <v>0</v>
       </c>
       <c r="FF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG12" t="n">
         <v>-0</v>
       </c>
       <c r="FH12" t="n">
-        <v>-0.007951328725751605</v>
+        <v>-0.09609457480039875</v>
       </c>
       <c r="FI12" t="n">
         <v>-0</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.07355083781046444</v>
+        <v>0.07588584510139673</v>
       </c>
       <c r="FK12" t="n">
-        <v>-0.03928235362515194</v>
+        <v>-0.004855250358317891</v>
       </c>
       <c r="FL12" t="n">
         <v>-0</v>
@@ -7196,49 +7196,49 @@
         <v>0</v>
       </c>
       <c r="FN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP12" t="n">
         <v>-0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>0.005791024024032932</v>
+        <v>0.00496066672948477</v>
       </c>
       <c r="FR12" t="n">
         <v>-0</v>
       </c>
       <c r="FS12" t="n">
-        <v>0.04791921909036771</v>
+        <v>0.05097066510454915</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.02430528777726926</v>
+        <v>-0.01054324346865373</v>
       </c>
       <c r="FU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX12" t="n">
         <v>0</v>
       </c>
       <c r="FY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>-0.02122629837673087</v>
+        <v>-0.1191297257632182</v>
       </c>
       <c r="GA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB12" t="n">
-        <v>-0.06772288014899247</v>
+        <v>0.04151415424333329</v>
       </c>
       <c r="GC12" t="n">
         <v>0</v>
@@ -7250,10 +7250,10 @@
         <v>-0</v>
       </c>
       <c r="GF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -7261,19 +7261,19 @@
         <v>0</v>
       </c>
       <c r="B13" t="n">
-        <v>0.6210226878725502</v>
+        <v>0.4585156283807222</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.03397600605017412</v>
+        <v>-0.017803152729276</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.7567874442112152</v>
+        <v>-0.1934048132633278</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -7288,25 +7288,25 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.562222865126364</v>
+        <v>0.6760396497274647</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>0.01165671668318147</v>
+        <v>-0.131131640763072</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.6914598576538218</v>
+        <v>-0.1562791827801858</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -7315,19 +7315,19 @@
         <v>-0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1132768080239878</v>
+        <v>0.129402378178797</v>
       </c>
       <c r="U13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.008764969091100304</v>
+        <v>-0.1113113747369525</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.006459526343970962</v>
+        <v>0.004805710563117789</v>
       </c>
       <c r="Y13" t="n">
         <v>-0</v>
@@ -7342,49 +7342,49 @@
         <v>-0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.07246621380519487</v>
+        <v>0.01380806060982256</v>
       </c>
       <c r="AD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.02240794245729293</v>
+        <v>-0.1969741150277859</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.001552114297804442</v>
+        <v>-0.06924236680279409</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI13" t="n">
         <v>-0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
         <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.04242638223720997</v>
+        <v>0.04738332400103701</v>
       </c>
       <c r="AM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
         <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.02767623744436835</v>
+        <v>0.01147077114292095</v>
       </c>
       <c r="AP13" t="n">
-        <v>-0.152651058809301</v>
+        <v>-0.04244574032354768</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR13" t="n">
         <v>-0</v>
@@ -7393,10 +7393,10 @@
         <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.5488980713453179</v>
+        <v>0.6785642411309663</v>
       </c>
       <c r="AV13" t="n">
         <v>-0</v>
@@ -7405,37 +7405,37 @@
         <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>-0.1051032089268411</v>
+        <v>-0.1414319694150896</v>
       </c>
       <c r="AY13" t="n">
-        <v>-0.5735930607046273</v>
+        <v>-0.1608204652823647</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
         <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.2499791294537516</v>
+        <v>0.002726853764090446</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF13" t="n">
         <v>0</v>
       </c>
       <c r="BG13" t="n">
-        <v>-0.1007381268241592</v>
+        <v>-0.07659094833524804</v>
       </c>
       <c r="BH13" t="n">
-        <v>-0.2212694270765937</v>
+        <v>-0.07705915096134996</v>
       </c>
       <c r="BI13" t="n">
         <v>0</v>
@@ -7444,31 +7444,31 @@
         <v>-0</v>
       </c>
       <c r="BK13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.1851551152036123</v>
+        <v>0.07497139413660846</v>
       </c>
       <c r="BN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.06894261414692239</v>
+        <v>0.1019312907940263</v>
       </c>
       <c r="BQ13" t="n">
-        <v>-0.01529146898677115</v>
+        <v>-0.05988317586853546</v>
       </c>
       <c r="BR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT13" t="n">
         <v>0</v>
@@ -7477,7 +7477,7 @@
         <v>-0</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.2953824561883292</v>
+        <v>0.4519340911281906</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
@@ -7486,10 +7486,10 @@
         <v>0</v>
       </c>
       <c r="BY13" t="n">
-        <v>-0.0408085823370525</v>
+        <v>-0.04571321343998968</v>
       </c>
       <c r="BZ13" t="n">
-        <v>-0.240807483263299</v>
+        <v>-0.07940403395075053</v>
       </c>
       <c r="CA13" t="n">
         <v>-0</v>
@@ -7501,28 +7501,28 @@
         <v>0</v>
       </c>
       <c r="CD13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE13" t="n">
-        <v>-0.1449005746284844</v>
+        <v>-0.1827779906920406</v>
       </c>
       <c r="CF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG13" t="n">
         <v>-0</v>
       </c>
       <c r="CH13" t="n">
-        <v>-0.03244853917710522</v>
+        <v>0.01526849907402072</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.1480043086938391</v>
+        <v>0.08031662235358082</v>
       </c>
       <c r="CJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL13" t="n">
         <v>-0</v>
@@ -7531,22 +7531,22 @@
         <v>0</v>
       </c>
       <c r="CN13" t="n">
-        <v>-0.06931264677373283</v>
+        <v>-0.2782196660394707</v>
       </c>
       <c r="CO13" t="n">
         <v>-0</v>
       </c>
       <c r="CP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.1691194439351825</v>
+        <v>0.1205935694412272</v>
       </c>
       <c r="CR13" t="n">
-        <v>-0.04338740554868777</v>
+        <v>0.1324836040769823</v>
       </c>
       <c r="CS13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT13" t="n">
         <v>-0</v>
@@ -7555,82 +7555,82 @@
         <v>-0</v>
       </c>
       <c r="CV13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW13" t="n">
-        <v>-0.1097038908828759</v>
+        <v>-0.183789891767765</v>
       </c>
       <c r="CX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY13" t="n">
         <v>0</v>
       </c>
       <c r="CZ13" t="n">
-        <v>-0.006732206488401272</v>
+        <v>-0.01448517541150976</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.1353952156517762</v>
+        <v>0.08654838746075456</v>
       </c>
       <c r="DB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD13" t="n">
         <v>0</v>
       </c>
       <c r="DE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF13" t="n">
-        <v>-0.1440784946098854</v>
+        <v>-0.08893300328464591</v>
       </c>
       <c r="DG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.07074678371188875</v>
+        <v>-0.1941716769481718</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.009838955780332885</v>
+        <v>0.04349208725620927</v>
       </c>
       <c r="DK13" t="n">
         <v>0</v>
       </c>
       <c r="DL13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM13" t="n">
         <v>0</v>
       </c>
       <c r="DN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO13" t="n">
-        <v>-0.03226174984015906</v>
+        <v>-0.1319078677640293</v>
       </c>
       <c r="DP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR13" t="n">
-        <v>-0.03602677167568526</v>
+        <v>0.08058976519930716</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.051266096792479</v>
+        <v>-0.0277909086843878</v>
       </c>
       <c r="DT13" t="n">
         <v>0</v>
       </c>
       <c r="DU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV13" t="n">
         <v>-0</v>
@@ -7639,19 +7639,19 @@
         <v>-0</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.09899261679539442</v>
+        <v>0.02782131457889257</v>
       </c>
       <c r="DY13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ13" t="n">
         <v>0</v>
       </c>
       <c r="EA13" t="n">
-        <v>-0.07592905305324234</v>
+        <v>0.1555887609887391</v>
       </c>
       <c r="EB13" t="n">
-        <v>-0.008783536908942138</v>
+        <v>-0.1865154923072042</v>
       </c>
       <c r="EC13" t="n">
         <v>-0</v>
@@ -7660,28 +7660,28 @@
         <v>0</v>
       </c>
       <c r="EE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG13" t="n">
-        <v>-0.09424225015705751</v>
+        <v>-0.04851265534637463</v>
       </c>
       <c r="EH13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI13" t="n">
         <v>0</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.03094541342894665</v>
+        <v>-0.06417001863241872</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.1178016082855579</v>
+        <v>0.03379276564995148</v>
       </c>
       <c r="EL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM13" t="n">
         <v>-0</v>
@@ -7690,22 +7690,22 @@
         <v>-0</v>
       </c>
       <c r="EO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP13" t="n">
-        <v>-0.04156647977713161</v>
+        <v>-0.02866655438910596</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER13" t="n">
         <v>-0</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.02266359652726366</v>
+        <v>-0.08580042112478625</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.01795451529244863</v>
+        <v>0.08381624078880358</v>
       </c>
       <c r="EU13" t="n">
         <v>-0</v>
@@ -7714,13 +7714,13 @@
         <v>0</v>
       </c>
       <c r="EW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY13" t="n">
-        <v>-0.114412885637465</v>
+        <v>-0.2128780168274191</v>
       </c>
       <c r="EZ13" t="n">
         <v>0</v>
@@ -7729,13 +7729,13 @@
         <v>-0</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.01514212284378945</v>
+        <v>-0.02453261173842101</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.1424384421869545</v>
+        <v>0.08215829782674254</v>
       </c>
       <c r="FD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE13" t="n">
         <v>0</v>
@@ -7747,34 +7747,34 @@
         <v>0</v>
       </c>
       <c r="FH13" t="n">
-        <v>-0.03909115138570707</v>
+        <v>-0.2213581819220997</v>
       </c>
       <c r="FI13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ13" t="n">
         <v>-0</v>
       </c>
       <c r="FK13" t="n">
-        <v>-0.04437860526973636</v>
+        <v>0.1431227694421806</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.1818885322827478</v>
+        <v>0.006785746712163418</v>
       </c>
       <c r="FM13" t="n">
         <v>0</v>
       </c>
       <c r="FN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ13" t="n">
-        <v>0.00268019177321826</v>
+        <v>0.001840131431580369</v>
       </c>
       <c r="FR13" t="n">
         <v>0</v>
@@ -7783,10 +7783,10 @@
         <v>-0</v>
       </c>
       <c r="FT13" t="n">
-        <v>-0.007739387973438859</v>
+        <v>-0.004293064496396348</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.1380565463242215</v>
+        <v>-0.01434648382844791</v>
       </c>
       <c r="FV13" t="n">
         <v>-0</v>
@@ -7795,13 +7795,13 @@
         <v>-0</v>
       </c>
       <c r="FX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ13" t="n">
-        <v>-0.03858794510161433</v>
+        <v>-0.06469756238551164</v>
       </c>
       <c r="GA13" t="n">
         <v>0</v>
@@ -7810,10 +7810,10 @@
         <v>-0</v>
       </c>
       <c r="GC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD13" t="n">
-        <v>-0.1540874237883813</v>
+        <v>-0.006661383506028275</v>
       </c>
       <c r="GE13" t="n">
         <v>-0</v>
@@ -7830,16 +7830,16 @@
         <v>0</v>
       </c>
       <c r="B14" t="n">
-        <v>0.8784934581476807</v>
+        <v>0.5537066628059077</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.3632865287636806</v>
+        <v>-0.3113461477554801</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.2248922723634346</v>
+        <v>-0.0923626771005155</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -7854,19 +7854,19 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K14" t="n">
-        <v>0.667692948103378</v>
+        <v>0.6503987366762102</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.322985945665113</v>
+        <v>-0.4131580725723147</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.2557062293686096</v>
+        <v>-0.1519601156630545</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -7884,70 +7884,70 @@
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2231983815271107</v>
+        <v>0.1365111791536264</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.1008623259267356</v>
+        <v>-0.1309927057132179</v>
       </c>
       <c r="W14" t="n">
-        <v>0.004839791885194015</v>
+        <v>-0.1524698074286496</v>
       </c>
       <c r="X14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
         <v>-0</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.08466915721936188</v>
+        <v>-0.04921883545896785</v>
       </c>
       <c r="AD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>-0.0125986813783856</v>
+        <v>-0.1349103405823947</v>
       </c>
       <c r="AF14" t="n">
-        <v>-0.01663031354347864</v>
+        <v>-0.1573223393736481</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.06298746954663333</v>
+        <v>0.1037205708822368</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN14" t="n">
-        <v>-0.0529915708467612</v>
+        <v>-0.09351935179733821</v>
       </c>
       <c r="AO14" t="n">
-        <v>-0.0353813705713008</v>
+        <v>0.03497916561340224</v>
       </c>
       <c r="AP14" t="n">
         <v>0</v>
@@ -7962,46 +7962,46 @@
         <v>0</v>
       </c>
       <c r="AT14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.812116094114221</v>
+        <v>0.7241939572633517</v>
       </c>
       <c r="AV14" t="n">
         <v>-0</v>
       </c>
       <c r="AW14" t="n">
-        <v>-0.01941901359731898</v>
+        <v>-0.1900294720474773</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.04515933109721324</v>
+        <v>-0.2782014623168343</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC14" t="n">
         <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.08281901896371821</v>
+        <v>-0.09204054625460914</v>
       </c>
       <c r="BE14" t="n">
         <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>-0.1311615139574133</v>
+        <v>-0.06588148475902722</v>
       </c>
       <c r="BG14" t="n">
-        <v>-0.389242919738926</v>
+        <v>-0.08886693620304909</v>
       </c>
       <c r="BH14" t="n">
         <v>0</v>
@@ -8010,55 +8010,55 @@
         <v>-0</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK14" t="n">
         <v>0</v>
       </c>
       <c r="BL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.1097960188254559</v>
+        <v>0.005169818089102534</v>
       </c>
       <c r="BN14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.06087328312717201</v>
+        <v>0.009424616635372243</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.117868959231277</v>
+        <v>0.1046276484693692</v>
       </c>
       <c r="BQ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT14" t="n">
         <v>-0</v>
       </c>
       <c r="BU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.4237428654196316</v>
+        <v>0.4820340769416118</v>
       </c>
       <c r="BW14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX14" t="n">
-        <v>-0.01445339187650892</v>
+        <v>-0.2394322821155811</v>
       </c>
       <c r="BY14" t="n">
-        <v>0.02775046906981214</v>
+        <v>-0.1022653702379997</v>
       </c>
       <c r="BZ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA14" t="n">
         <v>-0</v>
@@ -8073,46 +8073,46 @@
         <v>-0</v>
       </c>
       <c r="CE14" t="n">
-        <v>-0.1949584814341741</v>
+        <v>-0.2287650268043945</v>
       </c>
       <c r="CF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG14" t="n">
-        <v>0.05761840536665838</v>
+        <v>0.1628176951521411</v>
       </c>
       <c r="CH14" t="n">
-        <v>-0.0270871951726543</v>
+        <v>0.04475083829137758</v>
       </c>
       <c r="CI14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK14" t="n">
         <v>0</v>
       </c>
       <c r="CL14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM14" t="n">
         <v>0</v>
       </c>
       <c r="CN14" t="n">
-        <v>0.01191040913146814</v>
+        <v>-0.2272582348798993</v>
       </c>
       <c r="CO14" t="n">
         <v>-0</v>
       </c>
       <c r="CP14" t="n">
-        <v>-0.1742537896514579</v>
+        <v>0.3645794225540485</v>
       </c>
       <c r="CQ14" t="n">
-        <v>-0.1088994297313329</v>
+        <v>0.117206162534893</v>
       </c>
       <c r="CR14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS14" t="n">
         <v>-0</v>
@@ -8121,55 +8121,55 @@
         <v>-0</v>
       </c>
       <c r="CU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW14" t="n">
-        <v>-0.1697543472672373</v>
+        <v>-0.2137720258757046</v>
       </c>
       <c r="CX14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY14" t="n">
-        <v>0.09204475129255589</v>
+        <v>0.1824141781417336</v>
       </c>
       <c r="CZ14" t="n">
-        <v>-0.04645635700801658</v>
+        <v>0.02633576488131517</v>
       </c>
       <c r="DA14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC14" t="n">
         <v>-0</v>
       </c>
       <c r="DD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE14" t="n">
         <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>-0.1051658871587665</v>
+        <v>-0.1292263528009031</v>
       </c>
       <c r="DG14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH14" t="n">
-        <v>0.08706854729312663</v>
+        <v>0.02803315745904648</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.01954656916539991</v>
+        <v>-0.1428924826371614</v>
       </c>
       <c r="DJ14" t="n">
         <v>-0</v>
       </c>
       <c r="DK14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL14" t="n">
         <v>0</v>
@@ -8178,28 +8178,28 @@
         <v>0</v>
       </c>
       <c r="DN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO14" t="n">
-        <v>-0.09192302563160079</v>
+        <v>-0.09993567169888738</v>
       </c>
       <c r="DP14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ14" t="n">
-        <v>0.01291286724003654</v>
+        <v>-0.01556750108216737</v>
       </c>
       <c r="DR14" t="n">
-        <v>-0.10360699874252</v>
+        <v>-0.03962910438119669</v>
       </c>
       <c r="DS14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT14" t="n">
         <v>-0</v>
       </c>
       <c r="DU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV14" t="n">
         <v>0</v>
@@ -8208,52 +8208,52 @@
         <v>-0</v>
       </c>
       <c r="DX14" t="n">
-        <v>0.02722489626226264</v>
+        <v>0.1462723638982408</v>
       </c>
       <c r="DY14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ14" t="n">
-        <v>0.01567783788378933</v>
+        <v>0.1228797205278899</v>
       </c>
       <c r="EA14" t="n">
-        <v>-0.1000466493413481</v>
+        <v>-0.02076089230316922</v>
       </c>
       <c r="EB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED14" t="n">
         <v>0</v>
       </c>
       <c r="EE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF14" t="n">
         <v>0</v>
       </c>
       <c r="EG14" t="n">
-        <v>-0.1473988258712312</v>
+        <v>-0.1460348283372752</v>
       </c>
       <c r="EH14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI14" t="n">
-        <v>0.04810583724801406</v>
+        <v>0.1009971404896869</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.08787744887703648</v>
+        <v>0.0895168236390235</v>
       </c>
       <c r="EK14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN14" t="n">
         <v>-0</v>
@@ -8262,22 +8262,22 @@
         <v>0</v>
       </c>
       <c r="EP14" t="n">
-        <v>-0.08756905096977009</v>
+        <v>-0.06509837828643462</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER14" t="n">
-        <v>0.06231822913511581</v>
+        <v>0.1407589684668473</v>
       </c>
       <c r="ES14" t="n">
-        <v>-0.04389178704914584</v>
+        <v>-0.06505001326643944</v>
       </c>
       <c r="ET14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV14" t="n">
         <v>0</v>
@@ -8286,46 +8286,46 @@
         <v>-0</v>
       </c>
       <c r="EX14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY14" t="n">
-        <v>-0.1628706956030161</v>
+        <v>-0.2556094087551904</v>
       </c>
       <c r="EZ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA14" t="n">
-        <v>0.07425304832544696</v>
+        <v>0.1946037135845684</v>
       </c>
       <c r="FB14" t="n">
-        <v>-0.02931076681931715</v>
+        <v>0.01750903859788535</v>
       </c>
       <c r="FC14" t="n">
         <v>-0</v>
       </c>
       <c r="FD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE14" t="n">
         <v>0</v>
       </c>
       <c r="FF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG14" t="n">
         <v>0</v>
       </c>
       <c r="FH14" t="n">
-        <v>-0.08446876752561351</v>
+        <v>-0.1310025082598958</v>
       </c>
       <c r="FI14" t="n">
         <v>-0</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.09820007864899524</v>
+        <v>0.1102593197194506</v>
       </c>
       <c r="FK14" t="n">
-        <v>-0.07463899848275354</v>
+        <v>0.01829245733350324</v>
       </c>
       <c r="FL14" t="n">
         <v>-0</v>
@@ -8337,22 +8337,22 @@
         <v>-0</v>
       </c>
       <c r="FO14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ14" t="n">
-        <v>0.0006084882998351671</v>
+        <v>0.001181681537579309</v>
       </c>
       <c r="FR14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS14" t="n">
-        <v>0.06239735755131569</v>
+        <v>0.2135141040684968</v>
       </c>
       <c r="FT14" t="n">
-        <v>-0.002830360518424346</v>
+        <v>-0.006222504701551794</v>
       </c>
       <c r="FU14" t="n">
         <v>-0</v>
@@ -8367,28 +8367,28 @@
         <v>0</v>
       </c>
       <c r="FY14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ14" t="n">
-        <v>0.01276935988364448</v>
+        <v>-0.1889963071045989</v>
       </c>
       <c r="GA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB14" t="n">
-        <v>-0.04893091662871488</v>
+        <v>0.1444192899397705</v>
       </c>
       <c r="GC14" t="n">
         <v>0</v>
       </c>
       <c r="GD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE14" t="n">
         <v>-0</v>
       </c>
       <c r="GF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG14" t="n">
         <v>-0</v>
@@ -8399,7 +8399,7 @@
         <v>-0</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.7582469138063264</v>
+        <v>-0.4371235012767976</v>
       </c>
       <c r="C15" t="n">
         <v>-0</v>
@@ -8408,10 +8408,10 @@
         <v>-0</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1502828379137385</v>
+        <v>-0.02406830723707033</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9271320145538063</v>
+        <v>0.4306677231023531</v>
       </c>
       <c r="G15" t="n">
         <v>-0</v>
@@ -8426,19 +8426,19 @@
         <v>-0</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.5575181237584812</v>
+        <v>-0.4970474072324269</v>
       </c>
       <c r="L15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
         <v>-0</v>
       </c>
       <c r="N15" t="n">
-        <v>0.04023194604521934</v>
+        <v>0.1382938992233796</v>
       </c>
       <c r="O15" t="n">
-        <v>0.9399590424948375</v>
+        <v>0.4238764437378133</v>
       </c>
       <c r="P15" t="n">
         <v>-0</v>
@@ -8453,19 +8453,19 @@
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1029825930578165</v>
+        <v>-0.1833521224445047</v>
       </c>
       <c r="U15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
         <v>-0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.09034169379687541</v>
+        <v>0.1716146720911706</v>
       </c>
       <c r="X15" t="n">
-        <v>0.1004556828791519</v>
+        <v>0.0578933333813112</v>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
@@ -8477,10 +8477,10 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC15" t="n">
-        <v>-0.1175669772030323</v>
+        <v>-0.0158388799003307</v>
       </c>
       <c r="AD15" t="n">
         <v>-0</v>
@@ -8489,10 +8489,10 @@
         <v>-0</v>
       </c>
       <c r="AF15" t="n">
-        <v>-0.02046148771754353</v>
+        <v>0.2807256547594891</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.04904609708117562</v>
+        <v>0.1546807462915067</v>
       </c>
       <c r="AH15" t="n">
         <v>-0</v>
@@ -8507,19 +8507,19 @@
         <v>-0</v>
       </c>
       <c r="AL15" t="n">
-        <v>-0.08114298603847225</v>
+        <v>-0.1669657591069283</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN15" t="n">
         <v>-0</v>
       </c>
       <c r="AO15" t="n">
-        <v>-0.05714123408217611</v>
+        <v>-0.06652167719734962</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.1187828820322711</v>
+        <v>0.137518290822297</v>
       </c>
       <c r="AQ15" t="n">
         <v>0</v>
@@ -8534,34 +8534,34 @@
         <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>-0.6579068200356435</v>
+        <v>-0.8676116674337339</v>
       </c>
       <c r="AV15" t="n">
         <v>0</v>
       </c>
       <c r="AW15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.1442601174436599</v>
+        <v>0.07721350912427842</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.7643466410773879</v>
+        <v>0.274373848509149</v>
       </c>
       <c r="AZ15" t="n">
         <v>-0</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD15" t="n">
-        <v>-0.2649341018698691</v>
+        <v>0.1703983050877648</v>
       </c>
       <c r="BE15" t="n">
         <v>-0</v>
@@ -8570,10 +8570,10 @@
         <v>-0</v>
       </c>
       <c r="BG15" t="n">
-        <v>0.1193300525715137</v>
+        <v>0.2612548744277752</v>
       </c>
       <c r="BH15" t="n">
-        <v>0.2046606588403565</v>
+        <v>0.1757985399891939</v>
       </c>
       <c r="BI15" t="n">
         <v>-0</v>
@@ -8588,19 +8588,19 @@
         <v>0</v>
       </c>
       <c r="BM15" t="n">
-        <v>-0.2453811969043066</v>
+        <v>-0.07529190478810792</v>
       </c>
       <c r="BN15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO15" t="n">
         <v>0</v>
       </c>
       <c r="BP15" t="n">
-        <v>-0.07954983134803806</v>
+        <v>-0.1719132362575122</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0.06113506338423458</v>
+        <v>-0.01457864078032096</v>
       </c>
       <c r="BR15" t="n">
         <v>-0</v>
@@ -8615,19 +8615,19 @@
         <v>0</v>
       </c>
       <c r="BV15" t="n">
-        <v>-0.2690005074903601</v>
+        <v>-0.3837165099620769</v>
       </c>
       <c r="BW15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX15" t="n">
         <v>-0</v>
       </c>
       <c r="BY15" t="n">
-        <v>0.1119355566667957</v>
+        <v>0.08989714627985901</v>
       </c>
       <c r="BZ15" t="n">
-        <v>0.4717132841327888</v>
+        <v>0.2823096998672862</v>
       </c>
       <c r="CA15" t="n">
         <v>0</v>
@@ -8636,28 +8636,28 @@
         <v>0</v>
       </c>
       <c r="CC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE15" t="n">
-        <v>0.1594972755392999</v>
+        <v>0.188398209281701</v>
       </c>
       <c r="CF15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG15" t="n">
         <v>0</v>
       </c>
       <c r="CH15" t="n">
-        <v>-0.004912003063876068</v>
+        <v>-0.03385258400417801</v>
       </c>
       <c r="CI15" t="n">
-        <v>-0.1963644360621079</v>
+        <v>-0.1558954347103353</v>
       </c>
       <c r="CJ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK15" t="n">
         <v>-0</v>
@@ -8669,7 +8669,7 @@
         <v>-0</v>
       </c>
       <c r="CN15" t="n">
-        <v>0.07407688704368517</v>
+        <v>0.3487843099324474</v>
       </c>
       <c r="CO15" t="n">
         <v>-0</v>
@@ -8678,13 +8678,13 @@
         <v>0</v>
       </c>
       <c r="CQ15" t="n">
-        <v>-0.06715690857338044</v>
+        <v>-0.2384427660662415</v>
       </c>
       <c r="CR15" t="n">
-        <v>-0.02935212661760396</v>
+        <v>-0.216629179114519</v>
       </c>
       <c r="CS15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT15" t="n">
         <v>0</v>
@@ -8693,25 +8693,25 @@
         <v>0</v>
       </c>
       <c r="CV15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW15" t="n">
-        <v>0.1223265855114148</v>
+        <v>0.1731235922617229</v>
       </c>
       <c r="CX15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY15" t="n">
         <v>-0</v>
       </c>
       <c r="CZ15" t="n">
-        <v>-0.01128380152853223</v>
+        <v>-0.01256282333131307</v>
       </c>
       <c r="DA15" t="n">
-        <v>-0.2048388997097988</v>
+        <v>-0.1528969327979298</v>
       </c>
       <c r="DB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC15" t="n">
         <v>0</v>
@@ -8723,46 +8723,46 @@
         <v>-0</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.05872657309774387</v>
+        <v>0.02725620609333407</v>
       </c>
       <c r="DG15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DI15" t="n">
-        <v>-0.08085626342726829</v>
+        <v>0.1943455822641778</v>
       </c>
       <c r="DJ15" t="n">
-        <v>0.02781468789619927</v>
+        <v>-0.009005871846760979</v>
       </c>
       <c r="DK15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO15" t="n">
-        <v>0.01398013998446728</v>
+        <v>0.09724036368842535</v>
       </c>
       <c r="DP15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ15" t="n">
         <v>-0</v>
       </c>
       <c r="DR15" t="n">
-        <v>-0.008540061385034483</v>
+        <v>-0.05303411303182699</v>
       </c>
       <c r="DS15" t="n">
-        <v>-0.04948019180814339</v>
+        <v>-0.02776540769686243</v>
       </c>
       <c r="DT15" t="n">
         <v>0</v>
@@ -8771,28 +8771,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX15" t="n">
-        <v>-0.09468024319323173</v>
+        <v>-0.07974366813084312</v>
       </c>
       <c r="DY15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA15" t="n">
-        <v>0.07667255647422519</v>
+        <v>0.02728688838651624</v>
       </c>
       <c r="EB15" t="n">
-        <v>-0.0461987348719358</v>
+        <v>-0.07760341498347077</v>
       </c>
       <c r="EC15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED15" t="n">
         <v>-0</v>
@@ -8801,22 +8801,22 @@
         <v>0</v>
       </c>
       <c r="EF15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG15" t="n">
-        <v>0.1218900055042303</v>
+        <v>0.03961638279629112</v>
       </c>
       <c r="EH15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ15" t="n">
-        <v>-0.07296061888143247</v>
+        <v>0.08125136386751747</v>
       </c>
       <c r="EK15" t="n">
-        <v>-0.2109575061600869</v>
+        <v>-0.02548277861087456</v>
       </c>
       <c r="EL15" t="n">
         <v>0</v>
@@ -8825,13 +8825,13 @@
         <v>-0</v>
       </c>
       <c r="EN15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP15" t="n">
-        <v>0.06395440078264474</v>
+        <v>0.05603393684170243</v>
       </c>
       <c r="EQ15" t="n">
         <v>-0</v>
@@ -8840,40 +8840,40 @@
         <v>0</v>
       </c>
       <c r="ES15" t="n">
-        <v>-0.0492669958728409</v>
+        <v>0.09963998135613286</v>
       </c>
       <c r="ET15" t="n">
-        <v>0.02577217979895547</v>
+        <v>-0.1003916408041556</v>
       </c>
       <c r="EU15" t="n">
         <v>-0</v>
       </c>
       <c r="EV15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY15" t="n">
-        <v>0.1195850503722346</v>
+        <v>0.2046316022898013</v>
       </c>
       <c r="EZ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA15" t="n">
         <v>0</v>
       </c>
       <c r="FB15" t="n">
-        <v>-0.03730809181241014</v>
+        <v>0.009162277995748105</v>
       </c>
       <c r="FC15" t="n">
-        <v>-0.1905153150761364</v>
+        <v>-0.1418849144682578</v>
       </c>
       <c r="FD15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE15" t="n">
         <v>-0</v>
@@ -8885,7 +8885,7 @@
         <v>-0</v>
       </c>
       <c r="FH15" t="n">
-        <v>0.05054463459901462</v>
+        <v>0.2277434220959422</v>
       </c>
       <c r="FI15" t="n">
         <v>0</v>
@@ -8894,25 +8894,25 @@
         <v>0</v>
       </c>
       <c r="FK15" t="n">
-        <v>0.03420163781723273</v>
+        <v>-0.05693302263670699</v>
       </c>
       <c r="FL15" t="n">
-        <v>0.2009995146791851</v>
+        <v>0.236455937564275</v>
       </c>
       <c r="FM15" t="n">
         <v>-0</v>
       </c>
       <c r="FN15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO15" t="n">
         <v>-0</v>
       </c>
       <c r="FP15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ15" t="n">
-        <v>0.01668966067330652</v>
+        <v>0.0586318007818978</v>
       </c>
       <c r="FR15" t="n">
         <v>0</v>
@@ -8921,46 +8921,46 @@
         <v>0</v>
       </c>
       <c r="FT15" t="n">
-        <v>0.001070786628369367</v>
+        <v>0.0001984320679915498</v>
       </c>
       <c r="FU15" t="n">
-        <v>-0.1143702272758454</v>
+        <v>-0.2026361238353598</v>
       </c>
       <c r="FV15" t="n">
         <v>0</v>
       </c>
       <c r="FW15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ15" t="n">
-        <v>-0.0168502600608431</v>
+        <v>0.08090237683713537</v>
       </c>
       <c r="GA15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB15" t="n">
         <v>0</v>
       </c>
       <c r="GC15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD15" t="n">
-        <v>0.09023357006364424</v>
+        <v>0.04353505953097326</v>
       </c>
       <c r="GE15" t="n">
         <v>0</v>
       </c>
       <c r="GF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="16">
@@ -8968,49 +8968,49 @@
         <v>0</v>
       </c>
       <c r="B16" t="n">
-        <v>0.6066138665529329</v>
+        <v>0.3807820340654174</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.3170313451784009</v>
+        <v>-0.2166479685224378</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.08819419162418775</v>
+        <v>0.02007161171591568</v>
       </c>
       <c r="F16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H16" t="n">
         <v>-0</v>
       </c>
       <c r="I16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5308203455018886</v>
+        <v>0.4473875402622344</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.3194733189280368</v>
+        <v>-0.3062861523254922</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1351840295587689</v>
+        <v>-0.03068389123140634</v>
       </c>
       <c r="O16" t="n">
         <v>-0</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -9022,70 +9022,70 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1436642418041592</v>
+        <v>0.07869695684674488</v>
       </c>
       <c r="U16" t="n">
         <v>-0</v>
       </c>
       <c r="V16" t="n">
-        <v>0.009895618936870978</v>
+        <v>-0.01279102809863453</v>
       </c>
       <c r="W16" t="n">
-        <v>0.1437861102506199</v>
+        <v>-0.07465366819173219</v>
       </c>
       <c r="X16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
         <v>-0</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.1407657325925685</v>
+        <v>0.01278376918761865</v>
       </c>
       <c r="AD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.02032552770039113</v>
+        <v>-0.1520031360495961</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.04508699667666013</v>
+        <v>0.002327987784743708</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
         <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.005942071012516868</v>
+        <v>0.06645953486357144</v>
       </c>
       <c r="AM16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>-0.05987088096231129</v>
+        <v>-0.02139946459225725</v>
       </c>
       <c r="AO16" t="n">
-        <v>-0.06215676234881465</v>
+        <v>0.01403581705347425</v>
       </c>
       <c r="AP16" t="n">
         <v>0</v>
@@ -9094,25 +9094,25 @@
         <v>-0</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.4998375727761785</v>
+        <v>0.3210454171555405</v>
       </c>
       <c r="AV16" t="n">
         <v>-0</v>
       </c>
       <c r="AW16" t="n">
-        <v>-0.06507844702840632</v>
+        <v>-0.1363902410142125</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.1615230236700083</v>
+        <v>-0.2327632974733389</v>
       </c>
       <c r="AY16" t="n">
         <v>-0</v>
@@ -9121,55 +9121,55 @@
         <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
         <v>-0</v>
       </c>
       <c r="BC16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>0.07449554751060181</v>
+        <v>0.02138835128388342</v>
       </c>
       <c r="BE16" t="n">
         <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>-0.1494946969177984</v>
+        <v>-0.1027317160026049</v>
       </c>
       <c r="BG16" t="n">
-        <v>-0.1467073819784359</v>
+        <v>0.05820320194190012</v>
       </c>
       <c r="BH16" t="n">
         <v>0</v>
       </c>
       <c r="BI16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.09079010993690093</v>
+        <v>0.005022245023769021</v>
       </c>
       <c r="BN16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO16" t="n">
-        <v>0.02872359178941541</v>
+        <v>0.0139936136326582</v>
       </c>
       <c r="BP16" t="n">
-        <v>0.2994612261803915</v>
+        <v>0.06318197040361669</v>
       </c>
       <c r="BQ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR16" t="n">
         <v>0</v>
@@ -9184,16 +9184,16 @@
         <v>0</v>
       </c>
       <c r="BV16" t="n">
-        <v>0.2280461807480862</v>
+        <v>0.2206748959362733</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>0.01764160848282272</v>
+        <v>-0.07823107685749912</v>
       </c>
       <c r="BY16" t="n">
-        <v>0.1192189373331396</v>
+        <v>-0.05453925343409906</v>
       </c>
       <c r="BZ16" t="n">
         <v>0</v>
@@ -9202,31 +9202,31 @@
         <v>-0</v>
       </c>
       <c r="CB16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD16" t="n">
         <v>0</v>
       </c>
       <c r="CE16" t="n">
-        <v>-0.145398603114674</v>
+        <v>-0.1114502659063819</v>
       </c>
       <c r="CF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG16" t="n">
-        <v>0.03226544850955268</v>
+        <v>0.1133101793382598</v>
       </c>
       <c r="CH16" t="n">
-        <v>-0.007207931263310892</v>
+        <v>-0.01806941047266914</v>
       </c>
       <c r="CI16" t="n">
         <v>0</v>
       </c>
       <c r="CJ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK16" t="n">
         <v>0</v>
@@ -9238,49 +9238,49 @@
         <v>0</v>
       </c>
       <c r="CN16" t="n">
-        <v>-0.05566592721864749</v>
+        <v>-0.1065199178747483</v>
       </c>
       <c r="CO16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP16" t="n">
-        <v>-0.1593827258296742</v>
+        <v>0.2188033307139344</v>
       </c>
       <c r="CQ16" t="n">
-        <v>-0.1668808896215442</v>
+        <v>0.02148898570983873</v>
       </c>
       <c r="CR16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS16" t="n">
         <v>-0</v>
       </c>
       <c r="CT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW16" t="n">
-        <v>-0.1315285444038893</v>
+        <v>-0.0996666408760883</v>
       </c>
       <c r="CX16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY16" t="n">
-        <v>0.06527734924100229</v>
+        <v>0.1221363595651216</v>
       </c>
       <c r="CZ16" t="n">
-        <v>-0.008612991262216886</v>
+        <v>-0.01694012108829439</v>
       </c>
       <c r="DA16" t="n">
         <v>-0</v>
       </c>
       <c r="DB16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC16" t="n">
         <v>-0</v>
@@ -9292,16 +9292,16 @@
         <v>0</v>
       </c>
       <c r="DF16" t="n">
-        <v>-0.07057669978353451</v>
+        <v>-0.06085233060121768</v>
       </c>
       <c r="DG16" t="n">
         <v>0</v>
       </c>
       <c r="DH16" t="n">
-        <v>0.03880797028120846</v>
+        <v>0.06651746498230642</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.01634738492385569</v>
+        <v>-0.11759905433696</v>
       </c>
       <c r="DJ16" t="n">
         <v>-0</v>
@@ -9316,133 +9316,133 @@
         <v>0</v>
       </c>
       <c r="DN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO16" t="n">
-        <v>-0.03775590361102826</v>
+        <v>-0.08853451104429802</v>
       </c>
       <c r="DP16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ16" t="n">
-        <v>-0.1857822695911832</v>
+        <v>0.06229906027689888</v>
       </c>
       <c r="DR16" t="n">
-        <v>-0.03164784836880533</v>
+        <v>-0.05470485032011335</v>
       </c>
       <c r="DS16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX16" t="n">
-        <v>-0.09657142041081633</v>
+        <v>-0.009622544868604855</v>
       </c>
       <c r="DY16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ16" t="n">
-        <v>0.008685243720313818</v>
+        <v>0.03135301319073351</v>
       </c>
       <c r="EA16" t="n">
-        <v>0.01918259206261722</v>
+        <v>-0.04498946350094256</v>
       </c>
       <c r="EB16" t="n">
         <v>0</v>
       </c>
       <c r="EC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF16" t="n">
         <v>0</v>
       </c>
       <c r="EG16" t="n">
-        <v>-0.1473573092622562</v>
+        <v>-0.05970403657173984</v>
       </c>
       <c r="EH16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI16" t="n">
-        <v>-0.1192650212984031</v>
+        <v>-0.1493788905232494</v>
       </c>
       <c r="EJ16" t="n">
-        <v>0.1271803764202674</v>
+        <v>-0.000938839984379442</v>
       </c>
       <c r="EK16" t="n">
         <v>0</v>
       </c>
       <c r="EL16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN16" t="n">
         <v>-0</v>
       </c>
       <c r="EO16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP16" t="n">
-        <v>-0.1381069298003292</v>
+        <v>-0.03631177220413784</v>
       </c>
       <c r="EQ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER16" t="n">
-        <v>0.06555399373771405</v>
+        <v>0.007382017311736983</v>
       </c>
       <c r="ES16" t="n">
-        <v>0.008333981484709135</v>
+        <v>-0.008249043636606744</v>
       </c>
       <c r="ET16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV16" t="n">
         <v>0</v>
       </c>
       <c r="EW16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX16" t="n">
         <v>0</v>
       </c>
       <c r="EY16" t="n">
-        <v>-0.1353040288955496</v>
+        <v>-0.129525931582738</v>
       </c>
       <c r="EZ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA16" t="n">
-        <v>0.03563599420892002</v>
+        <v>0.137592608166012</v>
       </c>
       <c r="FB16" t="n">
-        <v>0.01661037309829315</v>
+        <v>-0.02163514356195747</v>
       </c>
       <c r="FC16" t="n">
         <v>0</v>
       </c>
       <c r="FD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE16" t="n">
         <v>0</v>
@@ -9451,19 +9451,19 @@
         <v>-0</v>
       </c>
       <c r="FG16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH16" t="n">
-        <v>-0.05455321339319882</v>
+        <v>0.1039702661337421</v>
       </c>
       <c r="FI16" t="n">
         <v>-0</v>
       </c>
       <c r="FJ16" t="n">
-        <v>0.08401326600909939</v>
+        <v>0.1027798161950255</v>
       </c>
       <c r="FK16" t="n">
-        <v>0.04209106255096625</v>
+        <v>-0.0174826823846701</v>
       </c>
       <c r="FL16" t="n">
         <v>-0</v>
@@ -9472,31 +9472,31 @@
         <v>-0</v>
       </c>
       <c r="FN16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO16" t="n">
         <v>0</v>
       </c>
       <c r="FP16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ16" t="n">
-        <v>0.02353570179717874</v>
+        <v>-0.1399923383578674</v>
       </c>
       <c r="FR16" t="n">
         <v>-0</v>
       </c>
       <c r="FS16" t="n">
-        <v>0.06770084483129152</v>
+        <v>0.1531073321864995</v>
       </c>
       <c r="FT16" t="n">
-        <v>-0.02810309528155342</v>
+        <v>0.1861776906465886</v>
       </c>
       <c r="FU16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW16" t="n">
         <v>-0</v>
@@ -9505,19 +9505,19 @@
         <v>0</v>
       </c>
       <c r="FY16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ16" t="n">
-        <v>0.03254595730502925</v>
+        <v>-0.08127289807776153</v>
       </c>
       <c r="GA16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB16" t="n">
-        <v>-0.1242832640566904</v>
+        <v>0.0435281503489037</v>
       </c>
       <c r="GC16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD16" t="n">
         <v>-0</v>
@@ -9526,10 +9526,10 @@
         <v>-0</v>
       </c>
       <c r="GF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -9537,22 +9537,22 @@
         <v>0</v>
       </c>
       <c r="B17" t="n">
-        <v>1.564438317047245</v>
+        <v>0.05745599301583969</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.4801806277184326</v>
+        <v>-0.02590105445308199</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1890452435384416</v>
+        <v>0.0112972159680771</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.494708805700207</v>
+        <v>-0.01066196075769661</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -9564,22 +9564,22 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>1.209981519368658</v>
+        <v>0.0735930183929842</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.4204410705780985</v>
+        <v>-0.02847828199191605</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>0.09785050839096103</v>
+        <v>-0.01084505550691432</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.3328633595427843</v>
+        <v>-0.01951156469030927</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -9591,103 +9591,103 @@
         <v>-0</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2165332750795366</v>
+        <v>0.01589166105053721</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.07499926032030499</v>
+        <v>0.0135990355748754</v>
       </c>
       <c r="V17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1776313878391281</v>
+        <v>0.0001266281378650464</v>
       </c>
       <c r="X17" t="n">
         <v>-0</v>
       </c>
       <c r="Y17" t="n">
-        <v>-0.07331923528952451</v>
+        <v>0.001400895438430193</v>
       </c>
       <c r="Z17" t="n">
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.2790322122890453</v>
+        <v>0.01041331561347701</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.001372259844958498</v>
+        <v>-0.008624261698537368</v>
       </c>
       <c r="AE17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>-0.07150099419593633</v>
+        <v>-0.01689549369844816</v>
       </c>
       <c r="AG17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>-0.138787305884505</v>
+        <v>-0.01200551347666687</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK17" t="n">
         <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.08811771915752263</v>
+        <v>0.01256675353500063</v>
       </c>
       <c r="AM17" t="n">
-        <v>-0.1706905907885532</v>
+        <v>-0.002314740945130653</v>
       </c>
       <c r="AN17" t="n">
         <v>-0</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.04069368815832248</v>
+        <v>0.01507825910887135</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>-0.08947823088425422</v>
+        <v>-0.001436946400744978</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT17" t="n">
         <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.09545887715339</v>
+        <v>0.05474654998758541</v>
       </c>
       <c r="AV17" t="n">
-        <v>-0.1998562410680262</v>
+        <v>0.004110785839688999</v>
       </c>
       <c r="AW17" t="n">
         <v>-0</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.2856314659454346</v>
+        <v>0.002849001121785768</v>
       </c>
       <c r="AY17" t="n">
         <v>0</v>
       </c>
       <c r="AZ17" t="n">
-        <v>-0.5199470463582111</v>
+        <v>0.001951834748664035</v>
       </c>
       <c r="BA17" t="n">
         <v>0</v>
@@ -9699,106 +9699,106 @@
         <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>0.3989955449727013</v>
+        <v>-0.008205966054106317</v>
       </c>
       <c r="BE17" t="n">
-        <v>-0.2692374958422595</v>
+        <v>-0.02189973047129874</v>
       </c>
       <c r="BF17" t="n">
         <v>0</v>
       </c>
       <c r="BG17" t="n">
-        <v>-0.2923483248587809</v>
+        <v>-0.01113204251499955</v>
       </c>
       <c r="BH17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BI17" t="n">
-        <v>-0.1528470980650614</v>
+        <v>-0.003571505361928833</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL17" t="n">
         <v>-0</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.3263471204865697</v>
+        <v>0.001225130292445639</v>
       </c>
       <c r="BN17" t="n">
-        <v>-0.1298346154554442</v>
+        <v>0.003084474661151424</v>
       </c>
       <c r="BO17" t="n">
         <v>-0</v>
       </c>
       <c r="BP17" t="n">
-        <v>0.08789999925109804</v>
+        <v>0.01362437251510696</v>
       </c>
       <c r="BQ17" t="n">
         <v>-0</v>
       </c>
       <c r="BR17" t="n">
-        <v>-0.04669709556558666</v>
+        <v>-0.003103863388017901</v>
       </c>
       <c r="BS17" t="n">
         <v>-0</v>
       </c>
       <c r="BT17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU17" t="n">
         <v>-0</v>
       </c>
       <c r="BV17" t="n">
-        <v>0.4914415285149547</v>
+        <v>0.03656278799798156</v>
       </c>
       <c r="BW17" t="n">
-        <v>-0.4279927126647993</v>
+        <v>0.007611094177827162</v>
       </c>
       <c r="BX17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY17" t="n">
-        <v>0.1249258509080047</v>
+        <v>0.004107768333408052</v>
       </c>
       <c r="BZ17" t="n">
         <v>0</v>
       </c>
       <c r="CA17" t="n">
-        <v>-0.1579569588365553</v>
+        <v>9.989758170983501e-05</v>
       </c>
       <c r="CB17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC17" t="n">
         <v>0</v>
       </c>
       <c r="CD17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE17" t="n">
-        <v>-0.3186821127089485</v>
+        <v>-0.01861200595439398</v>
       </c>
       <c r="CF17" t="n">
-        <v>-0.03421977780409369</v>
+        <v>0.008119027513747787</v>
       </c>
       <c r="CG17" t="n">
         <v>-0</v>
       </c>
       <c r="CH17" t="n">
-        <v>-0.07194510508707196</v>
+        <v>-0.0020721209313867</v>
       </c>
       <c r="CI17" t="n">
         <v>-0</v>
       </c>
       <c r="CJ17" t="n">
-        <v>0.1530111888540693</v>
+        <v>0.005226449569253167</v>
       </c>
       <c r="CK17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL17" t="n">
         <v>-0</v>
@@ -9807,52 +9807,52 @@
         <v>0</v>
       </c>
       <c r="CN17" t="n">
-        <v>-0.137263232489205</v>
+        <v>-0.02172582499881515</v>
       </c>
       <c r="CO17" t="n">
-        <v>-0.06240121999471192</v>
+        <v>0.003519176254257037</v>
       </c>
       <c r="CP17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ17" t="n">
-        <v>0.02892581498849759</v>
+        <v>0.01181232477103921</v>
       </c>
       <c r="CR17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS17" t="n">
-        <v>0.179538368998953</v>
+        <v>-0.004250211249512125</v>
       </c>
       <c r="CT17" t="n">
         <v>0</v>
       </c>
       <c r="CU17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV17" t="n">
         <v>-0</v>
       </c>
       <c r="CW17" t="n">
-        <v>-0.3033212719705656</v>
+        <v>-0.01945559927809472</v>
       </c>
       <c r="CX17" t="n">
-        <v>-0.07449594305099544</v>
+        <v>0.007371895705223045</v>
       </c>
       <c r="CY17" t="n">
         <v>0</v>
       </c>
       <c r="CZ17" t="n">
-        <v>-0.1344011694904067</v>
+        <v>-0.002468733617308145</v>
       </c>
       <c r="DA17" t="n">
         <v>0</v>
       </c>
       <c r="DB17" t="n">
-        <v>0.1580844449782692</v>
+        <v>0.006865930737869303</v>
       </c>
       <c r="DC17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD17" t="n">
         <v>0</v>
@@ -9861,106 +9861,106 @@
         <v>0</v>
       </c>
       <c r="DF17" t="n">
-        <v>-0.3536724259028195</v>
+        <v>-0.002860137173110163</v>
       </c>
       <c r="DG17" t="n">
-        <v>-0.006204648792383641</v>
+        <v>0.01488465688681556</v>
       </c>
       <c r="DH17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI17" t="n">
-        <v>-0.060259988363143</v>
+        <v>-0.03979473952379899</v>
       </c>
       <c r="DJ17" t="n">
         <v>-0</v>
       </c>
       <c r="DK17" t="n">
-        <v>0.0210118468540431</v>
+        <v>0.01199799611243325</v>
       </c>
       <c r="DL17" t="n">
         <v>-0</v>
       </c>
       <c r="DM17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN17" t="n">
         <v>0</v>
       </c>
       <c r="DO17" t="n">
-        <v>-0.05649437299007992</v>
+        <v>-0.008776076508668006</v>
       </c>
       <c r="DP17" t="n">
-        <v>-0.1114526293266669</v>
+        <v>-6.793050063084797e-05</v>
       </c>
       <c r="DQ17" t="n">
         <v>0</v>
       </c>
       <c r="DR17" t="n">
-        <v>0.08830062848053702</v>
+        <v>-0.009437012027808063</v>
       </c>
       <c r="DS17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.08112079857415852</v>
+        <v>0.006490892045839106</v>
       </c>
       <c r="DU17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW17" t="n">
         <v>-0</v>
       </c>
       <c r="DX17" t="n">
-        <v>-0.3829707278212361</v>
+        <v>-0.02244463841185462</v>
       </c>
       <c r="DY17" t="n">
-        <v>0.08988040317818283</v>
+        <v>-4.403199705817956e-05</v>
       </c>
       <c r="DZ17" t="n">
         <v>-0</v>
       </c>
       <c r="EA17" t="n">
-        <v>0.02139334406246612</v>
+        <v>0.00247428768261656</v>
       </c>
       <c r="EB17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC17" t="n">
-        <v>0.01022777002649513</v>
+        <v>-0.02048388370197648</v>
       </c>
       <c r="ED17" t="n">
         <v>0</v>
       </c>
       <c r="EE17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG17" t="n">
-        <v>-0.2094215133517111</v>
+        <v>-0.008441536777363194</v>
       </c>
       <c r="EH17" t="n">
-        <v>-0.0751992598559786</v>
+        <v>0.003533661049596536</v>
       </c>
       <c r="EI17" t="n">
         <v>-0</v>
       </c>
       <c r="EJ17" t="n">
-        <v>0.02883386057580396</v>
+        <v>0.002207337432006904</v>
       </c>
       <c r="EK17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL17" t="n">
-        <v>0.1823335743545391</v>
+        <v>-0.0002448950276274382</v>
       </c>
       <c r="EM17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN17" t="n">
         <v>-0</v>
@@ -9969,22 +9969,22 @@
         <v>0</v>
       </c>
       <c r="EP17" t="n">
-        <v>-0.2395092040907817</v>
+        <v>-0.008533557126157753</v>
       </c>
       <c r="EQ17" t="n">
-        <v>-0.07809687534093654</v>
+        <v>0.001909824818183563</v>
       </c>
       <c r="ER17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES17" t="n">
-        <v>-0.2093576233575279</v>
+        <v>0.005299179517855515</v>
       </c>
       <c r="ET17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU17" t="n">
-        <v>0.1584953785762921</v>
+        <v>0.0006711035245595779</v>
       </c>
       <c r="EV17" t="n">
         <v>0</v>
@@ -9993,52 +9993,52 @@
         <v>-0</v>
       </c>
       <c r="EX17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY17" t="n">
-        <v>-0.3011160281508934</v>
+        <v>-0.02280699265463884</v>
       </c>
       <c r="EZ17" t="n">
-        <v>-0.04327345722886523</v>
+        <v>0.006209481599814425</v>
       </c>
       <c r="FA17" t="n">
         <v>-0</v>
       </c>
       <c r="FB17" t="n">
-        <v>-0.09248276279494379</v>
+        <v>-0.002809870182389821</v>
       </c>
       <c r="FC17" t="n">
         <v>-0</v>
       </c>
       <c r="FD17" t="n">
-        <v>0.1662274786517847</v>
+        <v>0.004646773800656188</v>
       </c>
       <c r="FE17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG17" t="n">
         <v>0</v>
       </c>
       <c r="FH17" t="n">
-        <v>-0.06651316368909085</v>
+        <v>0.00744946017355361</v>
       </c>
       <c r="FI17" t="n">
-        <v>0.07865828543062567</v>
+        <v>0.0123539241673098</v>
       </c>
       <c r="FJ17" t="n">
         <v>-0</v>
       </c>
       <c r="FK17" t="n">
-        <v>0.2314182112156442</v>
+        <v>0.01597884408655009</v>
       </c>
       <c r="FL17" t="n">
         <v>-0</v>
       </c>
       <c r="FM17" t="n">
-        <v>-0.04436717279907224</v>
+        <v>-0.01088224271086708</v>
       </c>
       <c r="FN17" t="n">
         <v>-0</v>
@@ -10047,28 +10047,28 @@
         <v>0</v>
       </c>
       <c r="FP17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ17" t="n">
-        <v>-0.01515436951711765</v>
+        <v>-0.01551417556859531</v>
       </c>
       <c r="FR17" t="n">
-        <v>0.2668790984387312</v>
+        <v>-0.01077427603043528</v>
       </c>
       <c r="FS17" t="n">
         <v>-0</v>
       </c>
       <c r="FT17" t="n">
-        <v>0.0250451623023922</v>
+        <v>0.01897746818861833</v>
       </c>
       <c r="FU17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV17" t="n">
-        <v>-0.006270869217737728</v>
+        <v>0.002178207851813701</v>
       </c>
       <c r="FW17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX17" t="n">
         <v>0</v>
@@ -10077,28 +10077,28 @@
         <v>-0</v>
       </c>
       <c r="FZ17" t="n">
-        <v>0.1298720510504627</v>
+        <v>-0.02301280348783624</v>
       </c>
       <c r="GA17" t="n">
-        <v>-0.1569764348696804</v>
+        <v>-0.001161001891423945</v>
       </c>
       <c r="GB17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GC17" t="n">
         <v>0</v>
       </c>
       <c r="GD17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE17" t="n">
-        <v>-0.04847252923683373</v>
+        <v>-0.003977507845417367</v>
       </c>
       <c r="GF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -10106,61 +10106,61 @@
         <v>0</v>
       </c>
       <c r="B18" t="n">
-        <v>0.2043756583830827</v>
+        <v>0.5649541793306214</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.04386629843022957</v>
+        <v>0.0518395392227451</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1423386399395476</v>
+        <v>-0.3580925591703785</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H18" t="n">
         <v>-0</v>
       </c>
       <c r="I18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1741362742858704</v>
+        <v>0.7361786698378121</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.001209294562646114</v>
+        <v>-0.04057470249584846</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1026009948832638</v>
+        <v>-0.5174631300721676</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>0.01802108781063306</v>
+        <v>0.1877041745446287</v>
       </c>
       <c r="U18" t="n">
         <v>-0</v>
@@ -10169,16 +10169,16 @@
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.0197006392103806</v>
+        <v>-0.09562567772941262</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.002195803080451526</v>
+        <v>-0.1374899761708116</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA18" t="n">
         <v>-0</v>
@@ -10187,19 +10187,19 @@
         <v>-0</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.008892809872176093</v>
+        <v>0.01696368162247134</v>
       </c>
       <c r="AD18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.01689364405237849</v>
+        <v>-0.3536527136521438</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.008008990558974898</v>
+        <v>-0.01867562931029375</v>
       </c>
       <c r="AH18" t="n">
         <v>0</v>
@@ -10214,52 +10214,52 @@
         <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>0.01095924671996771</v>
+        <v>0.1395487148108705</v>
       </c>
       <c r="AM18" t="n">
         <v>-0</v>
       </c>
       <c r="AN18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.002654918504226958</v>
+        <v>-0.02745115041707313</v>
       </c>
       <c r="AP18" t="n">
-        <v>-0.04410392544052684</v>
+        <v>-0.0923696882900155</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR18" t="n">
         <v>-0</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT18" t="n">
         <v>0</v>
       </c>
       <c r="AU18" t="n">
-        <v>0.1259539729745685</v>
+        <v>0.9867073690744402</v>
       </c>
       <c r="AV18" t="n">
         <v>-0</v>
       </c>
       <c r="AW18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.002764515257635965</v>
+        <v>-0.3110455220739778</v>
       </c>
       <c r="AY18" t="n">
-        <v>-0.08132505891032485</v>
+        <v>-0.4353066529618462</v>
       </c>
       <c r="AZ18" t="n">
         <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB18" t="n">
         <v>-0</v>
@@ -10268,7 +10268,7 @@
         <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>0.03707386583091455</v>
+        <v>-0.1900642321771885</v>
       </c>
       <c r="BE18" t="n">
         <v>0</v>
@@ -10277,10 +10277,10 @@
         <v>0</v>
       </c>
       <c r="BG18" t="n">
-        <v>-0.04524203987361435</v>
+        <v>-0.03981455944538928</v>
       </c>
       <c r="BH18" t="n">
-        <v>-0.03998331147352147</v>
+        <v>0.04475565787948887</v>
       </c>
       <c r="BI18" t="n">
         <v>0</v>
@@ -10289,55 +10289,55 @@
         <v>-0</v>
       </c>
       <c r="BK18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL18" t="n">
         <v>0</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.0207085311600753</v>
+        <v>0.203735501876187</v>
       </c>
       <c r="BN18" t="n">
         <v>-0</v>
       </c>
       <c r="BO18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP18" t="n">
-        <v>0.02067480022039475</v>
+        <v>0.1205295419064986</v>
       </c>
       <c r="BQ18" t="n">
-        <v>0.00818180190937441</v>
+        <v>-0.03536935871282771</v>
       </c>
       <c r="BR18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS18" t="n">
         <v>-0</v>
       </c>
       <c r="BT18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV18" t="n">
-        <v>0.0656928213542245</v>
+        <v>0.4883827610786289</v>
       </c>
       <c r="BW18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY18" t="n">
-        <v>-0.007350013076157419</v>
+        <v>-0.07704506397963284</v>
       </c>
       <c r="BZ18" t="n">
-        <v>-0.02898002076486948</v>
+        <v>-0.2842484709845898</v>
       </c>
       <c r="CA18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB18" t="n">
         <v>-0</v>
@@ -10349,7 +10349,7 @@
         <v>0</v>
       </c>
       <c r="CE18" t="n">
-        <v>-0.03897308934490779</v>
+        <v>-0.2097487506088369</v>
       </c>
       <c r="CF18" t="n">
         <v>-0</v>
@@ -10358,13 +10358,13 @@
         <v>-0</v>
       </c>
       <c r="CH18" t="n">
-        <v>-0.005626518451781404</v>
+        <v>0.05739987348089028</v>
       </c>
       <c r="CI18" t="n">
-        <v>0.01774283698306015</v>
+        <v>0.09289972855996258</v>
       </c>
       <c r="CJ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK18" t="n">
         <v>0</v>
@@ -10376,7 +10376,7 @@
         <v>0</v>
       </c>
       <c r="CN18" t="n">
-        <v>-0.001975866403378715</v>
+        <v>-0.3816493044427596</v>
       </c>
       <c r="CO18" t="n">
         <v>-0</v>
@@ -10385,13 +10385,13 @@
         <v>-0</v>
       </c>
       <c r="CQ18" t="n">
-        <v>-0.01635127963026872</v>
+        <v>0.2528874134257927</v>
       </c>
       <c r="CR18" t="n">
-        <v>-0.0540555691439233</v>
+        <v>0.1162193615301228</v>
       </c>
       <c r="CS18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT18" t="n">
         <v>0</v>
@@ -10403,7 +10403,7 @@
         <v>-0</v>
       </c>
       <c r="CW18" t="n">
-        <v>-0.03798965313096233</v>
+        <v>-0.1946429791491124</v>
       </c>
       <c r="CX18" t="n">
         <v>0</v>
@@ -10412,10 +10412,10 @@
         <v>0</v>
       </c>
       <c r="CZ18" t="n">
-        <v>-0.005311105464013206</v>
+        <v>0.002203060703730397</v>
       </c>
       <c r="DA18" t="n">
-        <v>0.02437900009412021</v>
+        <v>0.128581418956033</v>
       </c>
       <c r="DB18" t="n">
         <v>0</v>
@@ -10430,34 +10430,34 @@
         <v>0</v>
       </c>
       <c r="DF18" t="n">
-        <v>-0.03008671881153499</v>
+        <v>-0.08290390003201333</v>
       </c>
       <c r="DG18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH18" t="n">
         <v>-0</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.0846566539949633</v>
+        <v>-0.1964315992440358</v>
       </c>
       <c r="DJ18" t="n">
-        <v>0.01629603818729655</v>
+        <v>0.03519065800207725</v>
       </c>
       <c r="DK18" t="n">
         <v>0</v>
       </c>
       <c r="DL18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO18" t="n">
-        <v>-0.00874622247519332</v>
+        <v>-0.07495130854173999</v>
       </c>
       <c r="DP18" t="n">
         <v>0</v>
@@ -10466,25 +10466,25 @@
         <v>0</v>
       </c>
       <c r="DR18" t="n">
-        <v>0.0241571508726516</v>
+        <v>0.04401229807229912</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.004733682220515316</v>
+        <v>0.1553008671253669</v>
       </c>
       <c r="DT18" t="n">
         <v>-0</v>
       </c>
       <c r="DU18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV18" t="n">
         <v>-0</v>
       </c>
       <c r="DW18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX18" t="n">
-        <v>-0.04080540800192708</v>
+        <v>-0.1833137485047188</v>
       </c>
       <c r="DY18" t="n">
         <v>-0</v>
@@ -10493,37 +10493,37 @@
         <v>-0</v>
       </c>
       <c r="EA18" t="n">
-        <v>0.009928465526109447</v>
+        <v>-0.08211147931993908</v>
       </c>
       <c r="EB18" t="n">
-        <v>-0.004313268092767705</v>
+        <v>-0.02312522333280378</v>
       </c>
       <c r="EC18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED18" t="n">
         <v>0</v>
       </c>
       <c r="EE18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF18" t="n">
         <v>0</v>
       </c>
       <c r="EG18" t="n">
-        <v>-0.0443123910977594</v>
+        <v>-0.02383379932494959</v>
       </c>
       <c r="EH18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI18" t="n">
         <v>-0</v>
       </c>
       <c r="EJ18" t="n">
-        <v>0.009214144144704065</v>
+        <v>-0.0347044476168711</v>
       </c>
       <c r="EK18" t="n">
-        <v>0.02178922133024143</v>
+        <v>-0.04823617862177482</v>
       </c>
       <c r="EL18" t="n">
         <v>-0</v>
@@ -10538,7 +10538,7 @@
         <v>0</v>
       </c>
       <c r="EP18" t="n">
-        <v>-0.03627471766878292</v>
+        <v>-0.1088431651110142</v>
       </c>
       <c r="EQ18" t="n">
         <v>-0</v>
@@ -10547,40 +10547,40 @@
         <v>-0</v>
       </c>
       <c r="ES18" t="n">
-        <v>-0.009948437523649793</v>
+        <v>-0.02525892889258948</v>
       </c>
       <c r="ET18" t="n">
-        <v>0.02759587708631538</v>
+        <v>0.04316413867920667</v>
       </c>
       <c r="EU18" t="n">
         <v>0</v>
       </c>
       <c r="EV18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX18" t="n">
         <v>0</v>
       </c>
       <c r="EY18" t="n">
-        <v>-0.03923548980168945</v>
+        <v>-0.2357631999511348</v>
       </c>
       <c r="EZ18" t="n">
         <v>-0</v>
       </c>
       <c r="FA18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB18" t="n">
-        <v>-0.001741497137267833</v>
+        <v>-0.004016884647356769</v>
       </c>
       <c r="FC18" t="n">
-        <v>0.02170056017024585</v>
+        <v>0.1121515531277381</v>
       </c>
       <c r="FD18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE18" t="n">
         <v>0</v>
@@ -10589,10 +10589,10 @@
         <v>-0</v>
       </c>
       <c r="FG18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH18" t="n">
-        <v>-0.01463236447843329</v>
+        <v>0.09213532179542021</v>
       </c>
       <c r="FI18" t="n">
         <v>0</v>
@@ -10601,10 +10601,10 @@
         <v>-0</v>
       </c>
       <c r="FK18" t="n">
-        <v>0.02507839036728543</v>
+        <v>-0.01166517028949099</v>
       </c>
       <c r="FL18" t="n">
-        <v>0.04223182923033963</v>
+        <v>0.2464454612475002</v>
       </c>
       <c r="FM18" t="n">
         <v>0</v>
@@ -10616,10 +10616,10 @@
         <v>0</v>
       </c>
       <c r="FP18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ18" t="n">
-        <v>0.001433456347121325</v>
+        <v>-0.1183201383233434</v>
       </c>
       <c r="FR18" t="n">
         <v>-0</v>
@@ -10628,46 +10628,46 @@
         <v>-0</v>
       </c>
       <c r="FT18" t="n">
-        <v>0.03244582343008491</v>
+        <v>0.3131015104153096</v>
       </c>
       <c r="FU18" t="n">
-        <v>0.03419933776438701</v>
+        <v>-0.05094644359943281</v>
       </c>
       <c r="FV18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX18" t="n">
         <v>0</v>
       </c>
       <c r="FY18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ18" t="n">
-        <v>-0.01726995570741145</v>
+        <v>-0.05879193227909165</v>
       </c>
       <c r="GA18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GC18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD18" t="n">
-        <v>-0.02903915527028985</v>
+        <v>0.11556667679125</v>
       </c>
       <c r="GE18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
